--- a/data/output/workbook/2026-07-06.xlsx
+++ b/data/output/workbook/2026-07-06.xlsx
@@ -427,7 +427,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10715625"/>
+    <ext cx="10125075" cy="10887075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -487,7 +487,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10839450"/>
+    <ext cx="10125075" cy="11106150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -547,7 +547,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10677525"/>
+    <ext cx="10125075" cy="11106150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06 11:56</t>
+          <t>2026-07-06 14:12</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,249 +1111,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>New York Mets offense vs Atlanta Braves defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>3.902</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>4.033</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H70" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>3.883</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.306</v>
+        <v>3.902</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.033</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>3.733</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.95</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>8</v>
+        <v>4.533</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>7.312</v>
+        <v>3.883</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>0.9389999999999999</v>
+        <v>7.306</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -1407,28 +1332,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.062</v>
+        <v>7.312</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.407999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -1482,319 +1407,319 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.561999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.407999999999999</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.561999999999999</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.526</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.35</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.067</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>0.1</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H75" s="33" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
         <is>
           <t>22nd</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Atlanta Braves offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>4.974</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H78" s="32" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>4.756</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.958</v>
+        <v>4.974</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.133</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J79" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>6.25</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>11</v>
+        <v>5.6</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>7.918</v>
+        <v>4.756</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.333</v>
+        <v>8.958</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>2.333</v>
+        <v>6.667</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -1848,28 +1773,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>0.918</v>
+        <v>7.918</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>7.688</v>
+        <v>1.333</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>6.667</v>
+        <v>2.333</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -1923,75 +1848,150 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.061</v>
+        <v>0.918</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>7.688</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>9.061</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.613</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.65</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>1.8</v>
       </c>
-      <c r="H82" s="32" t="inlineStr">
+      <c r="H83" s="32" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="J83" s="35" t="inlineStr">
         <is>
           <t>19th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.9</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.538</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -2938,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2955,251 +2955,174 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="28" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>Arizona Diamondbacks offense vs San Diego Padres defense</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D70" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E70" s="29" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F70" s="29" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G70" s="29" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H70" s="29" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I70" s="29" t="inlineStr">
+      <c r="I71" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J70" s="29" t="inlineStr">
+      <c r="J71" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K70" s="29" t="inlineStr">
+      <c r="K71" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L70" s="29" t="inlineStr">
+      <c r="L71" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M70" s="29" t="inlineStr">
+      <c r="M71" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N70" s="29" t="inlineStr">
+      <c r="N71" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O70" s="29" t="inlineStr">
+      <c r="O71" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P70" s="29" t="inlineStr">
+      <c r="P71" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q70" s="29" t="inlineStr">
+      <c r="Q71" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>4.351</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>3.633</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>6.133</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>4.229</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.542</v>
+        <v>4.351</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3.633</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H72" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>6.133</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>5.133</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>7.848</v>
+        <v>4.229</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>0.9379999999999999</v>
+        <v>8.542</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -3258,25 +3181,25 @@
         </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>0.848</v>
+        <v>7.848</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>7.354</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
@@ -3335,315 +3258,315 @@
         </is>
       </c>
       <c r="P74" s="31" t="n">
-        <v>8.304</v>
+        <v>0.848</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>7.354</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>8.304</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B75" s="31" t="n">
+      <c r="B76" s="31" t="n">
         <v>0.519</v>
       </c>
-      <c r="C75" s="31" t="n">
+      <c r="C76" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="D75" s="31" t="n">
+      <c r="D76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="E75" s="31" t="n">
+      <c r="E76" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="F75" s="31" t="n">
+      <c r="F76" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="G75" s="31" t="n">
+      <c r="G76" s="31" t="n">
         <v>1.4</v>
       </c>
-      <c r="H75" s="32" t="inlineStr">
+      <c r="H76" s="32" t="inlineStr">
         <is>
           <t>5th</t>
         </is>
       </c>
-      <c r="I75" s="31" t="inlineStr">
+      <c r="I76" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J75" s="35" t="inlineStr">
+      <c r="J76" s="35" t="inlineStr">
         <is>
           <t>16th</t>
         </is>
       </c>
-      <c r="K75" s="31" t="n">
+      <c r="K76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="L75" s="31" t="n">
+      <c r="L76" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="M75" s="31" t="n">
+      <c r="M76" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="N75" s="31" t="n">
+      <c r="N76" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="O75" s="31" t="n">
+      <c r="O76" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="P75" s="31" t="n">
+      <c r="P76" s="31" t="n">
         <v>0.474</v>
       </c>
-      <c r="Q75" s="34" t="inlineStr">
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>San Diego Padres offense vs Arizona Diamondbacks defense</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="29" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D78" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E78" s="29" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F78" s="29" t="inlineStr">
+      <c r="F79" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G78" s="29" t="inlineStr">
+      <c r="G79" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H78" s="29" t="inlineStr">
+      <c r="H79" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I78" s="29" t="inlineStr">
+      <c r="I79" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J78" s="29" t="inlineStr">
+      <c r="J79" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K78" s="29" t="inlineStr">
+      <c r="K79" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L78" s="29" t="inlineStr">
+      <c r="L79" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M78" s="29" t="inlineStr">
+      <c r="M79" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N78" s="29" t="inlineStr">
+      <c r="N79" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O78" s="29" t="inlineStr">
+      <c r="O79" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P78" s="29" t="inlineStr">
+      <c r="P79" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q78" s="29" t="inlineStr">
+      <c r="Q79" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C79" s="31" t="n">
-        <v>3.967</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="G79" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O79" s="31" t="n">
-        <v>4.967</v>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>4.506</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>7.087</v>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>4</v>
+      </c>
+      <c r="C80" s="31" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E80" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F80" s="31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G80" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H80" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L80" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M80" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="N80" s="31" t="n">
+        <v>4.55</v>
       </c>
       <c r="O80" s="31" t="n">
-        <v>10</v>
+        <v>4.967</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>8.188000000000001</v>
+        <v>4.506</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>1.022</v>
+        <v>7.087</v>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
@@ -3702,25 +3625,25 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>1.25</v>
+        <v>8.188000000000001</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>8.348000000000001</v>
+        <v>1.022</v>
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
@@ -3779,71 +3702,148 @@
         </is>
       </c>
       <c r="O82" s="31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>7.146</v>
+        <v>1.25</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>8.348000000000001</v>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="P83" s="31" t="n">
+        <v>7.146</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B83" s="31" t="n">
+      <c r="B84" s="31" t="n">
         <v>0.355</v>
       </c>
-      <c r="C83" s="31" t="n">
+      <c r="C84" s="31" t="n">
         <v>0.533</v>
       </c>
-      <c r="D83" s="31" t="n">
+      <c r="D84" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="E83" s="31" t="n">
+      <c r="E84" s="31" t="n">
         <v>0.267</v>
       </c>
-      <c r="F83" s="31" t="n">
+      <c r="F84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="G83" s="31" t="n">
+      <c r="G84" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H84" s="35" t="inlineStr">
         <is>
           <t>17th</t>
         </is>
       </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="32" t="inlineStr">
+      <c r="I84" s="31" t="inlineStr"/>
+      <c r="J84" s="32" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K83" s="31" t="n">
+      <c r="K84" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="31" t="n">
+      <c r="L84" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="M83" s="31" t="n">
+      <c r="M84" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N83" s="31" t="n">
+      <c r="N84" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="O83" s="31" t="n">
+      <c r="O84" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="P83" s="31" t="n">
+      <c r="P84" s="31" t="n">
         <v>0.623</v>
       </c>
-      <c r="Q83" s="34" t="inlineStr">
+      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4770,7 +4770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4787,328 +4787,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs Los Angeles Dodgers defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I71" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J71" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K71" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L71" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M71" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N71" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O71" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P71" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q71" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.925</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>6.596</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>0.92</v>
+        <v>4.925</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6.1</v>
+      </c>
+      <c r="D72" s="31" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E72" s="31" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="F72" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G72" s="31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H72" s="32" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>4.2</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>0.83</v>
+        <v>3.5</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.92</v>
+        <v>8.32</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5167,392 +5013,392 @@
         </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.106</v>
+        <v>6.596</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O75" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B76" s="31" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C76" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D76" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E76" s="31" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F76" s="31" t="n">
         <v>1.3</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G76" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H76" s="32" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr">
+      <c r="I76" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="J76" s="35" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L76" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M76" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N76" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O76" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P76" s="31" t="n">
         <v>0.468</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>Los Angeles Dodgers offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B79" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C79" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E79" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F79" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G79" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H79" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I79" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J79" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K79" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L79" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M79" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N79" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O79" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P79" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q79" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>5.463</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B79" s="31" t="n">
-        <v>9.191000000000001</v>
-      </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O79" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="P79" s="31" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="Q79" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="C80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.463</v>
+      </c>
+      <c r="C80" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D80" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E80" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F80" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G80" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H80" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J80" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L80" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M80" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N80" s="31" t="n">
+        <v>5.6</v>
       </c>
       <c r="O80" s="31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.24</v>
+        <v>5.65</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.510999999999999</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
@@ -5611,71 +5457,225 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.28</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B83" s="31" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O83" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P83" s="31" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q83" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B84" s="31" t="n">
         <v>0.623</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C84" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D84" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E84" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F84" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G84" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H84" s="33" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
+      <c r="I84" s="31" t="inlineStr"/>
+      <c r="J84" s="33" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K84" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L84" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M84" s="31" t="n">
         <v>0.867</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N84" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O84" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P84" s="31" t="n">
         <v>0.722</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5772,7 +5772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7067985611510791</v>
+        <v>0.7061510791366905</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-241</v>
+        <v>-240</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>178</v>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -241). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.6445555555555555</v>
+        <v>0.7074615384615384</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-181</v>
+        <v>-242</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 70.7% (fair -242). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -6090,17 +6090,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6110,17 +6110,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5860071942446042</v>
+        <v>0.6445555555555555</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-142</v>
+        <v>-181</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 64.5% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -6161,12 +6161,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5932584269662922</v>
+        <v>0.5837410071942446</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-146</v>
+        <v>-140</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -6227,32 +6227,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3749025974025974</v>
+        <v>0.5900374531835206</v>
       </c>
       <c r="G10" s="14" t="n">
+        <v>-144</v>
+      </c>
+      <c r="H10" s="15" t="n">
         <v>167</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>208</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -6288,17 +6288,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -6308,17 +6308,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres -1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4139928057553957</v>
+        <v>0.6305833333333333</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>142</v>
+        <v>-171</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -6359,12 +6359,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6306839285714286</v>
+        <v>0.5266812227074236</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-171</v>
+        <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-124</v>
+        <v>129</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -6440,17 +6440,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>San Diego Padres -1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5225242718446602</v>
+        <v>0.416241134751773</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-109</v>
+        <v>140</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -109). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -6491,32 +6491,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.406768060836502</v>
+        <v>0.3729392971246007</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>163</v>
+        <v>213</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -6557,32 +6557,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5005164319248827</v>
+        <v>0.6285101321585903</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-100</v>
+        <v>-169</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>113</v>
+        <v>-127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 62.9% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -6623,32 +6623,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5235643564356436</v>
+        <v>0.5279245283018867</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-110</v>
+        <v>-112</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -6684,37 +6684,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5173039215686274</v>
+        <v>0.5214423076923077</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-107</v>
+        <v>-109</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -6750,37 +6750,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5349882352941175</v>
+        <v>0.4099619771863118</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-115</v>
+        <v>144</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-104</v>
+        <v>163</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -6840,13 +6840,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.39893536121673</v>
+        <v>0.3974444444444444</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6902,17 +6902,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4893896713615024</v>
+        <v>0.5469576923076922</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>104</v>
+        <v>-121</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>-108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -6968,17 +6968,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5150495049504951</v>
+        <v>0.5257000000000001</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-106</v>
+        <v>-111</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -7014,37 +7014,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5551351851851852</v>
+        <v>0.4732882882882883</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-125</v>
+        <v>111</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-116</v>
+        <v>122</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -7100,17 +7100,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6163800000000001</v>
+        <v>0.5354470588235294</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-161</v>
+        <v>-115</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-150</v>
+        <v>-104</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -7146,17 +7146,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4680275229357799</v>
+        <v>0.4912206572769953</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -7209,9 +7209,339 @@
         <v/>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>0.5178712871287129</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>-107</v>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="I25" s="13">
+        <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
+        <v/>
+      </c>
+      <c r="J25" s="16">
+        <f>IF($H$25="","",$F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF($H$25="","",MAX(0,($F$25*IF($H$25&lt;0,-100/$H$25,$H$25/100)-(1-$F$25))/IF($H$25&lt;0,-100/$H$25,$H$25/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L25" s="18">
+        <f>IF($H$25="","",ROUND(MIN($K$25,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF($J$25="","",IF($J$25&lt;0,"Pass",IF($J$25&lt;'Settings'!$B$4,"Thin",IF($J$25&lt;0.06,"✅ Sharp band",IF($J$25&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.8% (fair -107). Your call.</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n"/>
+      <c r="P25" s="16">
+        <f>IF(OR($H$25="",$O$25=""),"",(1+IF($H$25&lt;0,-100/$H$25,$H$25/100))/(1+IF($O$25&lt;0,-100/$O$25,$O$25/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Under 9.5</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>-110</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.3% (fair -110). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Seattle Mariners @ Miami Marlins</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Miami Marlins</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.52055</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.1% (fair -109). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.6130032786885246</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>-158</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-144</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 61.3% (fair -158). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Athletics @ Detroit Tigers</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>22:40</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Over 8</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.5271372549019607</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.7% (fair -111). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J24">
+  <conditionalFormatting sqref="J5:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -7233,7 +7563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P88"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7377,13 +7707,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.653263829787234</v>
+        <v>0.6615795918367346</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-188</v>
+        <v>-195</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-182</v>
+        <v>-194</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -7407,7 +7737,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 65.3% (fair -188). Your call.</t>
+          <t>Model 66.2% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7443,13 +7773,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3467132867132867</v>
+        <v>0.3384228187919463</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7473,7 +7803,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 34.7% (fair +188). Your call.</t>
+          <t>Model 33.8% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7505,17 +7835,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3991</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>151</v>
+        <v>-130</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7539,7 +7869,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 56.5% (fair -130). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7571,17 +7901,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6009</v>
+        <v>0.4350000000000001</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-151</v>
+        <v>130</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7605,7 +7935,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 43.5% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7641,13 +7971,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4647465437788018</v>
+        <v>0.4732882882882883</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -7671,7 +8001,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -7707,13 +8037,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.535228310502283</v>
+        <v>0.5266812227074236</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-115</v>
+        <v>-111</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-119</v>
+        <v>129</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -7737,7 +8067,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -7773,13 +8103,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5235643564356436</v>
+        <v>0.5257000000000001</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-110</v>
+        <v>-111</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -7803,7 +8133,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -7839,13 +8169,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4764207920792079</v>
+        <v>0.4742980099502487</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -7869,7 +8199,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -7905,10 +8235,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5005164319248827</v>
+        <v>0.5514</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-100</v>
+        <v>-123</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>113</v>
@@ -7935,7 +8265,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -100). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -7971,13 +8301,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.499481220657277</v>
+        <v>0.4486</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-113</v>
+        <v>112</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8001,7 +8331,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8037,10 +8367,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2932142857142857</v>
+        <v>0.2938571428571429</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>180</v>
@@ -8067,7 +8397,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +241). Your call.</t>
+          <t>Model 29.4% (fair +240). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8103,10 +8433,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7067985611510791</v>
+        <v>0.7061510791366905</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-241</v>
+        <v>-240</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>178</v>
@@ -8133,7 +8463,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -241). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8169,13 +8499,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4801449275362318</v>
+        <v>0.480873786407767</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>108</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8199,7 +8529,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8235,7 +8565,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5198545893719807</v>
+        <v>0.5191309178743961</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-108</v>
@@ -8265,7 +8595,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8301,13 +8631,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5299</v>
+        <v>0.5476</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-113</v>
+        <v>-121</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8331,7 +8661,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8367,10 +8697,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4701</v>
+        <v>0.4524</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>113</v>
@@ -8397,7 +8727,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8433,10 +8763,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.406768060836502</v>
+        <v>0.4099619771863118</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>163</v>
@@ -8463,7 +8793,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.7% (fair +146). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8499,10 +8829,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5932584269662922</v>
+        <v>0.5900374531835206</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-146</v>
+        <v>-144</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>167</v>
@@ -8529,7 +8859,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.3% (fair -146). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8565,13 +8895,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4680275229357799</v>
+        <v>0.4674654377880184</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>114</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8595,7 +8925,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8631,13 +8961,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5319818181818182</v>
+        <v>0.5325135135135135</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-114</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -8661,7 +8991,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -8697,10 +9027,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.381</v>
+        <v>0.3786</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>125</v>
@@ -8727,7 +9057,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 38.1% (fair +162). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -8763,10 +9093,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.619</v>
+        <v>0.6214</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-162</v>
+        <v>-164</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>125</v>
@@ -8793,7 +9123,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 61.9% (fair -162). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -8829,13 +9159,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3692883895131086</v>
+        <v>0.3714828897338403</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -8859,7 +9189,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 37.1% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -8895,13 +9225,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6306839285714286</v>
+        <v>0.6285101321585903</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-171</v>
+        <v>-169</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-124</v>
+        <v>-127</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -8925,7 +9255,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 62.9% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -8961,13 +9291,13 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.49515</v>
+        <v>0.4976287128712871</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -8991,7 +9321,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9027,10 +9357,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.50485</v>
+        <v>0.50235</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-102</v>
+        <v>-101</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>100</v>
@@ -9057,7 +9387,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -9093,13 +9423,13 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5694</v>
+        <v>0.5555</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-132</v>
+        <v>-125</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -9123,7 +9453,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -9159,10 +9489,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4306</v>
+        <v>0.4445</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>115</v>
@@ -9189,7 +9519,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -9225,13 +9555,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4571830985915493</v>
+        <v>0.4547906976744186</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -9255,7 +9585,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -9291,13 +9621,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5428317757009345</v>
+        <v>0.5452069767441862</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -9321,7 +9651,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -9357,10 +9687,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.3387</v>
+        <v>0.3417</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>124</v>
@@ -9387,7 +9717,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 33.9% (fair +195). Your call.</t>
+          <t>Model 34.2% (fair +193). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -9423,13 +9753,13 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.6613</v>
+        <v>0.6583</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-195</v>
+        <v>-193</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -9453,7 +9783,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 66.1% (fair -195). Your call.</t>
+          <t>Model 65.8% (fair -193). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -9489,13 +9819,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4139928057553957</v>
+        <v>0.416241134751773</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -9519,7 +9849,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -9555,10 +9885,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5860071942446042</v>
+        <v>0.5837410071942446</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-142</v>
+        <v>-140</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>178</v>
@@ -9585,7 +9915,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -9621,13 +9951,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4849254901960784</v>
+        <v>0.4821</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -9651,7 +9981,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.5% (fair +106). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -9687,10 +10017,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5150495049504951</v>
+        <v>0.5178712871287129</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>102</v>
@@ -9717,7 +10047,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -9749,14 +10079,14 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.5035843137254902</v>
+        <v>0.472078431372549</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>-101</v>
+        <v>112</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>-104</v>
@@ -9783,7 +10113,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -9815,17 +10145,17 @@
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.496421568627451</v>
+        <v>0.5279245283018867</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>101</v>
+        <v>-112</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -9849,7 +10179,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -9885,13 +10215,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3749025974025974</v>
+        <v>0.3729392971246007</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -9915,7 +10245,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 37.3% (fair +168). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -9951,10 +10281,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6250602564102563</v>
+        <v>0.6270307692307692</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-167</v>
+        <v>-168</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>-212</v>
@@ -9981,7 +10311,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.7% (fair -168). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -10017,13 +10347,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4712</v>
+        <v>0.4727</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>106</v>
+        <v>-102</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -10047,7 +10377,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -10083,13 +10413,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5287999999999999</v>
+        <v>0.5273</v>
       </c>
       <c r="G46" s="14" t="n">
         <v>-112</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -10113,7 +10443,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -10149,13 +10479,13 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.4774681159420289</v>
+        <v>0.478575</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>109</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -10179,7 +10509,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +109). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -10215,13 +10545,13 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5225242718446602</v>
+        <v>0.5214423076923077</v>
       </c>
       <c r="G48" s="14" t="n">
         <v>-109</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -10245,7 +10575,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -109). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -11073,10 +11403,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5167531400966183</v>
+        <v>0.5183038647342995</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>-107</v>
@@ -11103,7 +11433,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -11139,10 +11469,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.483235294117647</v>
+        <v>0.4816666666666667</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>104</v>
@@ -11169,7 +11499,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -11186,32 +11516,32 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.39893536121673</v>
+        <v>0.4769756097560976</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -11235,7 +11565,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -11252,32 +11582,32 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.6010381294964029</v>
+        <v>0.523</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-151</v>
+        <v>-110</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>-178</v>
+        <v>100</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -11301,7 +11631,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -11318,32 +11648,32 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4397356828193832</v>
+        <v>0.6007121212121211</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>127</v>
+        <v>-150</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>127</v>
+        <v>-164</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -11367,7 +11697,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -11384,32 +11714,32 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5602657657657658</v>
+        <v>0.39925</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-127</v>
+        <v>150</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>-122</v>
+        <v>140</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -11433,7 +11763,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -11450,7 +11780,7 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -11465,17 +11795,17 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.4826823529411765</v>
+        <v>0.3974444444444444</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>-104</v>
+        <v>170</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -11499,7 +11829,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -11516,7 +11846,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
@@ -11531,17 +11861,17 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.5173039215686274</v>
+        <v>0.6025748201438849</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-107</v>
+        <v>-152</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>104</v>
+        <v>-178</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -11565,7 +11895,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -11582,7 +11912,7 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
@@ -11592,22 +11922,22 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.4893896713615024</v>
+        <v>0.5271372549019607</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>104</v>
+        <v>-111</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>113</v>
+        <v>-104</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -11631,7 +11961,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -11648,7 +11978,7 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
@@ -11658,22 +11988,22 @@
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.5106483870967742</v>
+        <v>0.4728428571428572</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>-104</v>
+        <v>111</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-117</v>
+        <v>-110</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -11697,7 +12027,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -11714,32 +12044,32 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4448598130841122</v>
+        <v>0.4406481481481481</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -11763,7 +12093,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -11780,32 +12110,32 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5551351851851852</v>
+        <v>0.5593888888888888</v>
       </c>
       <c r="G72" s="14" t="n">
+        <v>-127</v>
+      </c>
+      <c r="H72" s="15" t="n">
         <v>-125</v>
-      </c>
-      <c r="H72" s="15" t="n">
-        <v>-116</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -11829,7 +12159,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -11846,12 +12176,12 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -11861,17 +12191,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4309442060085837</v>
+        <v>0.4384581497797357</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -11895,7 +12225,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -11912,12 +12242,12 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
@@ -11927,17 +12257,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5690360655737705</v>
+        <v>0.5615297297297297</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-132</v>
+        <v>-128</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-144</v>
+        <v>-122</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -11961,7 +12291,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -11978,12 +12308,12 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -11993,17 +12323,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.6163800000000001</v>
+        <v>0.4794705882352941</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>-161</v>
+        <v>109</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-150</v>
+        <v>-104</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -12027,7 +12357,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -12044,12 +12374,12 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
@@ -12059,17 +12389,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.3836065573770492</v>
+        <v>0.52055</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>161</v>
+        <v>-109</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -12093,7 +12423,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -12110,12 +12440,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -12125,17 +12455,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4650490196078431</v>
+        <v>0.4912206572769953</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -12159,7 +12489,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -12176,12 +12506,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -12191,17 +12521,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5349882352941175</v>
+        <v>0.5087652582159624</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-115</v>
+        <v>-104</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-104</v>
+        <v>-113</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -12225,7 +12555,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -12242,12 +12572,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -12257,16 +12587,18 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4948</v>
+        <v>0.453047619047619</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>102</v>
-      </c>
-      <c r="H79" s="15" t="n"/>
+        <v>121</v>
+      </c>
+      <c r="H79" s="15" t="n">
+        <v>110</v>
+      </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
         <v/>
@@ -12289,7 +12621,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -12306,12 +12638,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -12321,16 +12653,18 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5052</v>
+        <v>0.5469576923076922</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H80" s="15" t="n"/>
+        <v>-121</v>
+      </c>
+      <c r="H80" s="15" t="n">
+        <v>-108</v>
+      </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
         <v/>
@@ -12353,7 +12687,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -12370,31 +12704,33 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4738</v>
+        <v>0.5161254901960783</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H81" s="15" t="n"/>
+        <v>-107</v>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>-104</v>
+      </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
         <v/>
@@ -12417,7 +12753,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -12434,31 +12770,33 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5262</v>
+        <v>0.4839024390243903</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H82" s="15" t="n"/>
+        <v>107</v>
+      </c>
+      <c r="H82" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
         <v/>
@@ -12481,7 +12819,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -12498,31 +12836,33 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Washington Nationals +1.5</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4053</v>
+        <v>0.7074615384615384</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>147</v>
-      </c>
-      <c r="H83" s="15" t="n"/>
+        <v>-242</v>
+      </c>
+      <c r="H83" s="15" t="n">
+        <v>160</v>
+      </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
         <v/>
@@ -12545,7 +12885,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 70.7% (fair -242). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -12562,31 +12902,33 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Houston Astros -1.5</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5947</v>
+        <v>0.2925572519083969</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-147</v>
-      </c>
-      <c r="H84" s="15" t="n"/>
+        <v>242</v>
+      </c>
+      <c r="H84" s="15" t="n">
+        <v>162</v>
+      </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
         <v/>
@@ -12609,7 +12951,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 29.3% (fair +242). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -12626,12 +12968,12 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -12641,16 +12983,18 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.462</v>
+        <v>0.4366094420600858</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="H85" s="15" t="n"/>
+        <v>129</v>
+      </c>
+      <c r="H85" s="15" t="n">
+        <v>133</v>
+      </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
         <v/>
@@ -12673,7 +13017,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -12690,12 +13034,12 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D86" s="20" t="inlineStr">
@@ -12705,16 +13049,18 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.538</v>
+        <v>0.5634295081967213</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-116</v>
-      </c>
-      <c r="H86" s="15" t="n"/>
+        <v>-129</v>
+      </c>
+      <c r="H86" s="15" t="n">
+        <v>-144</v>
+      </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
         <v/>
@@ -12737,7 +13083,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -12754,12 +13100,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -12769,16 +13115,18 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3802</v>
+        <v>0.6130032786885246</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>163</v>
-      </c>
-      <c r="H87" s="15" t="n"/>
+        <v>-158</v>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-144</v>
+      </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
         <v/>
@@ -12801,7 +13149,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 61.3% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -12818,12 +13166,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -12833,16 +13181,18 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6198</v>
+        <v>0.3870081967213115</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-163</v>
-      </c>
-      <c r="H88" s="15" t="n"/>
+        <v>158</v>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>144</v>
+      </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
         <v/>
@@ -12865,7 +13215,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 38.7% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -12874,9 +13224,1969 @@
         <v/>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Over 9.5</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="G89" s="14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H89" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I89" s="13">
+        <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
+        <v/>
+      </c>
+      <c r="J89" s="16">
+        <f>IF($H$89="","",$F$89*IF($H$89&lt;0,-100/$H$89,$H$89/100)-(1-$F$89))</f>
+        <v/>
+      </c>
+      <c r="K89" s="17">
+        <f>IF($H$89="","",MAX(0,($F$89*IF($H$89&lt;0,-100/$H$89,$H$89/100)-(1-$F$89))/IF($H$89&lt;0,-100/$H$89,$H$89/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L89" s="18">
+        <f>IF($H$89="","",ROUND(MIN($K$89,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M89" s="12">
+        <f>IF($J$89="","",IF($J$89&lt;0,"Pass",IF($J$89&lt;'Settings'!$B$4,"Thin",IF($J$89&lt;0.06,"✅ Sharp band",IF($J$89&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N89" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.6% (fair -103). Your call.</t>
+        </is>
+      </c>
+      <c r="O89" s="15" t="n"/>
+      <c r="P89" s="16">
+        <f>IF(OR($H$89="",$O$89=""),"",(1+IF($H$89&lt;0,-100/$H$89,$H$89/100))/(1+IF($O$89&lt;0,-100/$O$89,$O$89/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>Under 9.5</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>0.4934954954954955</v>
+      </c>
+      <c r="G90" s="14" t="n">
+        <v>103</v>
+      </c>
+      <c r="H90" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I90" s="13">
+        <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
+        <v/>
+      </c>
+      <c r="J90" s="16">
+        <f>IF($H$90="","",$F$90*IF($H$90&lt;0,-100/$H$90,$H$90/100)-(1-$F$90))</f>
+        <v/>
+      </c>
+      <c r="K90" s="17">
+        <f>IF($H$90="","",MAX(0,($F$90*IF($H$90&lt;0,-100/$H$90,$H$90/100)-(1-$F$90))/IF($H$90&lt;0,-100/$H$90,$H$90/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L90" s="18">
+        <f>IF($H$90="","",ROUND(MIN($K$90,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M90" s="12">
+        <f>IF($J$90="","",IF($J$90&lt;0,"Pass",IF($J$90&lt;'Settings'!$B$4,"Thin",IF($J$90&lt;0.06,"✅ Sharp band",IF($J$90&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N90" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.3% (fair +103). Your call.</t>
+        </is>
+      </c>
+      <c r="O90" s="15" t="n"/>
+      <c r="P90" s="16">
+        <f>IF(OR($H$90="",$O$90=""),"",(1+IF($H$90&lt;0,-100/$H$90,$H$90/100))/(1+IF($O$90&lt;0,-100/$O$90,$O$90/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="n">
+        <v>0.4645588235294117</v>
+      </c>
+      <c r="G91" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="H91" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="I91" s="13">
+        <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
+        <v/>
+      </c>
+      <c r="J91" s="16">
+        <f>IF($H$91="","",$F$91*IF($H$91&lt;0,-100/$H$91,$H$91/100)-(1-$F$91))</f>
+        <v/>
+      </c>
+      <c r="K91" s="17">
+        <f>IF($H$91="","",MAX(0,($F$91*IF($H$91&lt;0,-100/$H$91,$H$91/100)-(1-$F$91))/IF($H$91&lt;0,-100/$H$91,$H$91/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L91" s="18">
+        <f>IF($H$91="","",ROUND(MIN($K$91,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M91" s="12">
+        <f>IF($J$91="","",IF($J$91&lt;0,"Pass",IF($J$91&lt;'Settings'!$B$4,"Thin",IF($J$91&lt;0.06,"✅ Sharp band",IF($J$91&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N91" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.5% (fair +115). Your call.</t>
+        </is>
+      </c>
+      <c r="O91" s="15" t="n"/>
+      <c r="P91" s="16">
+        <f>IF(OR($H$91="",$O$91=""),"",(1+IF($H$91&lt;0,-100/$H$91,$H$91/100))/(1+IF($O$91&lt;0,-100/$O$91,$O$91/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>0.5354470588235294</v>
+      </c>
+      <c r="G92" s="14" t="n">
+        <v>-115</v>
+      </c>
+      <c r="H92" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I92" s="13">
+        <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
+        <v/>
+      </c>
+      <c r="J92" s="16">
+        <f>IF($H$92="","",$F$92*IF($H$92&lt;0,-100/$H$92,$H$92/100)-(1-$F$92))</f>
+        <v/>
+      </c>
+      <c r="K92" s="17">
+        <f>IF($H$92="","",MAX(0,($F$92*IF($H$92&lt;0,-100/$H$92,$H$92/100)-(1-$F$92))/IF($H$92&lt;0,-100/$H$92,$H$92/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L92" s="18">
+        <f>IF($H$92="","",ROUND(MIN($K$92,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M92" s="12">
+        <f>IF($J$92="","",IF($J$92&lt;0,"Pass",IF($J$92&lt;'Settings'!$B$4,"Thin",IF($J$92&lt;0.06,"✅ Sharp band",IF($J$92&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N92" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.5% (fair -115). Your call.</t>
+        </is>
+      </c>
+      <c r="O92" s="15" t="n"/>
+      <c r="P92" s="16">
+        <f>IF(OR($H$92="",$O$92=""),"",(1+IF($H$92&lt;0,-100/$H$92,$H$92/100))/(1+IF($O$92&lt;0,-100/$O$92,$O$92/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Over 8.5</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="n">
+        <v>0.5211904761904762</v>
+      </c>
+      <c r="G93" s="14" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H93" s="15" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I93" s="13">
+        <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
+        <v/>
+      </c>
+      <c r="J93" s="16">
+        <f>IF($H$93="","",$F$93*IF($H$93&lt;0,-100/$H$93,$H$93/100)-(1-$F$93))</f>
+        <v/>
+      </c>
+      <c r="K93" s="17">
+        <f>IF($H$93="","",MAX(0,($F$93*IF($H$93&lt;0,-100/$H$93,$H$93/100)-(1-$F$93))/IF($H$93&lt;0,-100/$H$93,$H$93/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L93" s="18">
+        <f>IF($H$93="","",ROUND(MIN($K$93,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M93" s="12">
+        <f>IF($J$93="","",IF($J$93&lt;0,"Pass",IF($J$93&lt;'Settings'!$B$4,"Thin",IF($J$93&lt;0.06,"✅ Sharp band",IF($J$93&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N93" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.1% (fair -109). Your call.</t>
+        </is>
+      </c>
+      <c r="O93" s="15" t="n"/>
+      <c r="P93" s="16">
+        <f>IF(OR($H$93="",$O$93=""),"",(1+IF($H$93&lt;0,-100/$H$93,$H$93/100))/(1+IF($O$93&lt;0,-100/$O$93,$O$93/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>Under 8.5</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>0.4788346153846154</v>
+      </c>
+      <c r="G94" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="H94" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I94" s="13">
+        <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
+        <v/>
+      </c>
+      <c r="J94" s="16">
+        <f>IF($H$94="","",$F$94*IF($H$94&lt;0,-100/$H$94,$H$94/100)-(1-$F$94))</f>
+        <v/>
+      </c>
+      <c r="K94" s="17">
+        <f>IF($H$94="","",MAX(0,($F$94*IF($H$94&lt;0,-100/$H$94,$H$94/100)-(1-$F$94))/IF($H$94&lt;0,-100/$H$94,$H$94/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L94" s="18">
+        <f>IF($H$94="","",ROUND(MIN($K$94,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M94" s="12">
+        <f>IF($J$94="","",IF($J$94&lt;0,"Pass",IF($J$94&lt;'Settings'!$B$4,"Thin",IF($J$94&lt;0.06,"✅ Sharp band",IF($J$94&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N94" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.9% (fair +109). Your call.</t>
+        </is>
+      </c>
+      <c r="O94" s="15" t="n"/>
+      <c r="P94" s="16">
+        <f>IF(OR($H$94="",$O$94=""),"",(1+IF($H$94&lt;0,-100/$H$94,$H$94/100))/(1+IF($O$94&lt;0,-100/$O$94,$O$94/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Minnesota Twins +1.5</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="n">
+        <v>0.6646704918032786</v>
+      </c>
+      <c r="G95" s="14" t="n">
+        <v>-198</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>-205</v>
+      </c>
+      <c r="I95" s="13">
+        <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
+        <v/>
+      </c>
+      <c r="J95" s="16">
+        <f>IF($H$95="","",$F$95*IF($H$95&lt;0,-100/$H$95,$H$95/100)-(1-$F$95))</f>
+        <v/>
+      </c>
+      <c r="K95" s="17">
+        <f>IF($H$95="","",MAX(0,($F$95*IF($H$95&lt;0,-100/$H$95,$H$95/100)-(1-$F$95))/IF($H$95&lt;0,-100/$H$95,$H$95/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L95" s="18">
+        <f>IF($H$95="","",ROUND(MIN($K$95,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M95" s="12">
+        <f>IF($J$95="","",IF($J$95&lt;0,"Pass",IF($J$95&lt;'Settings'!$B$4,"Thin",IF($J$95&lt;0.06,"✅ Sharp band",IF($J$95&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N95" s="19" t="inlineStr">
+        <is>
+          <t>Model 66.5% (fair -198). Your call.</t>
+        </is>
+      </c>
+      <c r="O95" s="15" t="n"/>
+      <c r="P95" s="16">
+        <f>IF(OR($H$95="",$O$95=""),"",(1+IF($H$95&lt;0,-100/$H$95,$H$95/100))/(1+IF($O$95&lt;0,-100/$O$95,$O$95/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians -1.5</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>0.3353358208955224</v>
+      </c>
+      <c r="G96" s="14" t="n">
+        <v>198</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>168</v>
+      </c>
+      <c r="I96" s="13">
+        <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
+        <v/>
+      </c>
+      <c r="J96" s="16">
+        <f>IF($H$96="","",$F$96*IF($H$96&lt;0,-100/$H$96,$H$96/100)-(1-$F$96))</f>
+        <v/>
+      </c>
+      <c r="K96" s="17">
+        <f>IF($H$96="","",MAX(0,($F$96*IF($H$96&lt;0,-100/$H$96,$H$96/100)-(1-$F$96))/IF($H$96&lt;0,-100/$H$96,$H$96/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L96" s="18">
+        <f>IF($H$96="","",ROUND(MIN($K$96,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M96" s="12">
+        <f>IF($J$96="","",IF($J$96&lt;0,"Pass",IF($J$96&lt;'Settings'!$B$4,"Thin",IF($J$96&lt;0.06,"✅ Sharp band",IF($J$96&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N96" s="19" t="inlineStr">
+        <is>
+          <t>Model 33.5% (fair +198). Your call.</t>
+        </is>
+      </c>
+      <c r="O96" s="15" t="n"/>
+      <c r="P96" s="16">
+        <f>IF(OR($H$96="",$O$96=""),"",(1+IF($H$96&lt;0,-100/$H$96,$H$96/100))/(1+IF($O$96&lt;0,-100/$O$96,$O$96/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="n">
+        <v>0.4973</v>
+      </c>
+      <c r="G97" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H97" s="15" t="n"/>
+      <c r="I97" s="13">
+        <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
+        <v/>
+      </c>
+      <c r="J97" s="16">
+        <f>IF($H$97="","",$F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))</f>
+        <v/>
+      </c>
+      <c r="K97" s="17">
+        <f>IF($H$97="","",MAX(0,($F$97*IF($H$97&lt;0,-100/$H$97,$H$97/100)-(1-$F$97))/IF($H$97&lt;0,-100/$H$97,$H$97/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L97" s="18">
+        <f>IF($H$97="","",ROUND(MIN($K$97,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M97" s="12">
+        <f>IF($J$97="","",IF($J$97&lt;0,"Pass",IF($J$97&lt;'Settings'!$B$4,"Thin",IF($J$97&lt;0.06,"✅ Sharp band",IF($J$97&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N97" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.7% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O97" s="15" t="n"/>
+      <c r="P97" s="16">
+        <f>IF(OR($H$97="",$O$97=""),"",(1+IF($H$97&lt;0,-100/$H$97,$H$97/100))/(1+IF($O$97&lt;0,-100/$O$97,$O$97/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>0.5027</v>
+      </c>
+      <c r="G98" s="14" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H98" s="15" t="n"/>
+      <c r="I98" s="13">
+        <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
+        <v/>
+      </c>
+      <c r="J98" s="16">
+        <f>IF($H$98="","",$F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))</f>
+        <v/>
+      </c>
+      <c r="K98" s="17">
+        <f>IF($H$98="","",MAX(0,($F$98*IF($H$98&lt;0,-100/$H$98,$H$98/100)-(1-$F$98))/IF($H$98&lt;0,-100/$H$98,$H$98/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L98" s="18">
+        <f>IF($H$98="","",ROUND(MIN($K$98,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M98" s="12">
+        <f>IF($J$98="","",IF($J$98&lt;0,"Pass",IF($J$98&lt;'Settings'!$B$4,"Thin",IF($J$98&lt;0.06,"✅ Sharp band",IF($J$98&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N98" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.3% (fair -101). Your call.</t>
+        </is>
+      </c>
+      <c r="O98" s="15" t="n"/>
+      <c r="P98" s="16">
+        <f>IF(OR($H$98="",$O$98=""),"",(1+IF($H$98&lt;0,-100/$H$98,$H$98/100))/(1+IF($O$98&lt;0,-100/$O$98,$O$98/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="inlineStr">
+        <is>
+          <t>Over 8</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="n">
+        <v>0.5113433962264151</v>
+      </c>
+      <c r="G99" s="14" t="n">
+        <v>-105</v>
+      </c>
+      <c r="H99" s="15" t="n">
+        <v>-112</v>
+      </c>
+      <c r="I99" s="13">
+        <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
+        <v/>
+      </c>
+      <c r="J99" s="16">
+        <f>IF($H$99="","",$F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))</f>
+        <v/>
+      </c>
+      <c r="K99" s="17">
+        <f>IF($H$99="","",MAX(0,($F$99*IF($H$99&lt;0,-100/$H$99,$H$99/100)-(1-$F$99))/IF($H$99&lt;0,-100/$H$99,$H$99/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L99" s="18">
+        <f>IF($H$99="","",ROUND(MIN($K$99,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M99" s="12">
+        <f>IF($J$99="","",IF($J$99&lt;0,"Pass",IF($J$99&lt;'Settings'!$B$4,"Thin",IF($J$99&lt;0.06,"✅ Sharp band",IF($J$99&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N99" s="19" t="inlineStr">
+        <is>
+          <t>Model 51.1% (fair -105). Your call.</t>
+        </is>
+      </c>
+      <c r="O99" s="15" t="n"/>
+      <c r="P99" s="16">
+        <f>IF(OR($H$99="",$O$99=""),"",(1+IF($H$99&lt;0,-100/$H$99,$H$99/100))/(1+IF($O$99&lt;0,-100/$O$99,$O$99/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>Under 8</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>0.4886853658536585</v>
+      </c>
+      <c r="G100" s="14" t="n">
+        <v>105</v>
+      </c>
+      <c r="H100" s="15" t="n">
+        <v>-105</v>
+      </c>
+      <c r="I100" s="13">
+        <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
+        <v/>
+      </c>
+      <c r="J100" s="16">
+        <f>IF($H$100="","",$F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))</f>
+        <v/>
+      </c>
+      <c r="K100" s="17">
+        <f>IF($H$100="","",MAX(0,($F$100*IF($H$100&lt;0,-100/$H$100,$H$100/100)-(1-$F$100))/IF($H$100&lt;0,-100/$H$100,$H$100/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L100" s="18">
+        <f>IF($H$100="","",ROUND(MIN($K$100,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M100" s="12">
+        <f>IF($J$100="","",IF($J$100&lt;0,"Pass",IF($J$100&lt;'Settings'!$B$4,"Thin",IF($J$100&lt;0.06,"✅ Sharp band",IF($J$100&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N100" s="19" t="inlineStr">
+        <is>
+          <t>Model 48.9% (fair +105). Your call.</t>
+        </is>
+      </c>
+      <c r="O100" s="15" t="n"/>
+      <c r="P100" s="16">
+        <f>IF(OR($H$100="",$O$100=""),"",(1+IF($H$100&lt;0,-100/$H$100,$H$100/100))/(1+IF($O$100&lt;0,-100/$O$100,$O$100/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Chicago White Sox -1.5</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.3694166666666667</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>171</v>
+      </c>
+      <c r="H101" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="I101" s="13">
+        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M101" s="12">
+        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Model 36.9% (fair +171). Your call.</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="16">
+        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox @ Chicago White Sox</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>23:40</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>Boston Red Sox +1.5</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>0.6305833333333333</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>-171</v>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="I102" s="13">
+        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M102" s="12">
+        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="19" t="inlineStr">
+        <is>
+          <t>Model 63.1% (fair -171). Your call.</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="16">
+        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="G103" s="14" t="n">
+        <v>111</v>
+      </c>
+      <c r="H103" s="15" t="n"/>
+      <c r="I103" s="13">
+        <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
+        <v/>
+      </c>
+      <c r="J103" s="16">
+        <f>IF($H$103="","",$F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF($H$103="","",MAX(0,($F$103*IF($H$103&lt;0,-100/$H$103,$H$103/100)-(1-$F$103))/IF($H$103&lt;0,-100/$H$103,$H$103/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L103" s="18">
+        <f>IF($H$103="","",ROUND(MIN($K$103,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M103" s="12">
+        <f>IF($J$103="","",IF($J$103&lt;0,"Pass",IF($J$103&lt;'Settings'!$B$4,"Thin",IF($J$103&lt;0.06,"✅ Sharp band",IF($J$103&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N103" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.4% (fair +111). Your call.</t>
+        </is>
+      </c>
+      <c r="O103" s="15" t="n"/>
+      <c r="P103" s="16">
+        <f>IF(OR($H$103="",$O$103=""),"",(1+IF($H$103&lt;0,-100/$H$103,$H$103/100))/(1+IF($O$103&lt;0,-100/$O$103,$O$103/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>Texas Rangers</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>0.5262</v>
+      </c>
+      <c r="G104" s="14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H104" s="15" t="n"/>
+      <c r="I104" s="13">
+        <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
+        <v/>
+      </c>
+      <c r="J104" s="16">
+        <f>IF($H$104="","",$F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))</f>
+        <v/>
+      </c>
+      <c r="K104" s="17">
+        <f>IF($H$104="","",MAX(0,($F$104*IF($H$104&lt;0,-100/$H$104,$H$104/100)-(1-$F$104))/IF($H$104&lt;0,-100/$H$104,$H$104/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L104" s="18">
+        <f>IF($H$104="","",ROUND(MIN($K$104,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M104" s="12">
+        <f>IF($J$104="","",IF($J$104&lt;0,"Pass",IF($J$104&lt;'Settings'!$B$4,"Thin",IF($J$104&lt;0.06,"✅ Sharp band",IF($J$104&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N104" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.6% (fair -111). Your call.</t>
+        </is>
+      </c>
+      <c r="O104" s="15" t="n"/>
+      <c r="P104" s="16">
+        <f>IF(OR($H$104="",$O$104=""),"",(1+IF($H$104&lt;0,-100/$H$104,$H$104/100))/(1+IF($O$104&lt;0,-100/$O$104,$O$104/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="inlineStr">
+        <is>
+          <t>Over 7</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="n">
+        <v>0.5567821428571429</v>
+      </c>
+      <c r="G105" s="14" t="n">
+        <v>-126</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>-124</v>
+      </c>
+      <c r="I105" s="13">
+        <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
+        <v/>
+      </c>
+      <c r="J105" s="16">
+        <f>IF($H$105="","",$F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))</f>
+        <v/>
+      </c>
+      <c r="K105" s="17">
+        <f>IF($H$105="","",MAX(0,($F$105*IF($H$105&lt;0,-100/$H$105,$H$105/100)-(1-$F$105))/IF($H$105&lt;0,-100/$H$105,$H$105/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L105" s="18">
+        <f>IF($H$105="","",ROUND(MIN($K$105,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M105" s="12">
+        <f>IF($J$105="","",IF($J$105&lt;0,"Pass",IF($J$105&lt;'Settings'!$B$4,"Thin",IF($J$105&lt;0.06,"✅ Sharp band",IF($J$105&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N105" s="19" t="inlineStr">
+        <is>
+          <t>Model 55.7% (fair -126). Your call.</t>
+        </is>
+      </c>
+      <c r="O105" s="15" t="n"/>
+      <c r="P105" s="16">
+        <f>IF(OR($H$105="",$O$105=""),"",(1+IF($H$105&lt;0,-100/$H$105,$H$105/100))/(1+IF($O$105&lt;0,-100/$O$105,$O$105/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>Under 7</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="n">
+        <v>0.4432178217821782</v>
+      </c>
+      <c r="G106" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="I106" s="13">
+        <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
+        <v/>
+      </c>
+      <c r="J106" s="16">
+        <f>IF($H$106="","",$F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))</f>
+        <v/>
+      </c>
+      <c r="K106" s="17">
+        <f>IF($H$106="","",MAX(0,($F$106*IF($H$106&lt;0,-100/$H$106,$H$106/100)-(1-$F$106))/IF($H$106&lt;0,-100/$H$106,$H$106/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L106" s="18">
+        <f>IF($H$106="","",ROUND(MIN($K$106,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M106" s="12">
+        <f>IF($J$106="","",IF($J$106&lt;0,"Pass",IF($J$106&lt;'Settings'!$B$4,"Thin",IF($J$106&lt;0.06,"✅ Sharp band",IF($J$106&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N106" s="19" t="inlineStr">
+        <is>
+          <t>Model 44.3% (fair +126). Your call.</t>
+        </is>
+      </c>
+      <c r="O106" s="15" t="n"/>
+      <c r="P106" s="16">
+        <f>IF(OR($H$106="",$O$106=""),"",(1+IF($H$106&lt;0,-100/$H$106,$H$106/100))/(1+IF($O$106&lt;0,-100/$O$106,$O$106/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Texas Rangers -1.5</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>0.4032478632478633</v>
+      </c>
+      <c r="G107" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="I107" s="13">
+        <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
+        <v/>
+      </c>
+      <c r="J107" s="16">
+        <f>IF($H$107="","",$F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))</f>
+        <v/>
+      </c>
+      <c r="K107" s="17">
+        <f>IF($H$107="","",MAX(0,($F$107*IF($H$107&lt;0,-100/$H$107,$H$107/100)-(1-$F$107))/IF($H$107&lt;0,-100/$H$107,$H$107/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L107" s="18">
+        <f>IF($H$107="","",ROUND(MIN($K$107,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M107" s="12">
+        <f>IF($J$107="","",IF($J$107&lt;0,"Pass",IF($J$107&lt;'Settings'!$B$4,"Thin",IF($J$107&lt;0.06,"✅ Sharp band",IF($J$107&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N107" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.3% (fair +148). Your call.</t>
+        </is>
+      </c>
+      <c r="O107" s="15" t="n"/>
+      <c r="P107" s="16">
+        <f>IF(OR($H$107="",$O$107=""),"",(1+IF($H$107&lt;0,-100/$H$107,$H$107/100))/(1+IF($O$107&lt;0,-100/$O$107,$O$107/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels @ Texas Rangers</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>00:05</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Angels +1.5</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>0.5967412213740457</v>
+      </c>
+      <c r="G108" s="14" t="n">
+        <v>-148</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-162</v>
+      </c>
+      <c r="I108" s="13">
+        <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
+        <v/>
+      </c>
+      <c r="J108" s="16">
+        <f>IF($H$108="","",$F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))</f>
+        <v/>
+      </c>
+      <c r="K108" s="17">
+        <f>IF($H$108="","",MAX(0,($F$108*IF($H$108&lt;0,-100/$H$108,$H$108/100)-(1-$F$108))/IF($H$108&lt;0,-100/$H$108,$H$108/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L108" s="18">
+        <f>IF($H$108="","",ROUND(MIN($K$108,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M108" s="12">
+        <f>IF($J$108="","",IF($J$108&lt;0,"Pass",IF($J$108&lt;'Settings'!$B$4,"Thin",IF($J$108&lt;0.06,"✅ Sharp band",IF($J$108&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N108" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.7% (fair -148). Your call.</t>
+        </is>
+      </c>
+      <c r="O108" s="15" t="n"/>
+      <c r="P108" s="16">
+        <f>IF(OR($H$108="",$O$108=""),"",(1+IF($H$108&lt;0,-100/$H$108,$H$108/100))/(1+IF($O$108&lt;0,-100/$O$108,$O$108/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="G109" s="14" t="n">
+        <v>147</v>
+      </c>
+      <c r="H109" s="15" t="n"/>
+      <c r="I109" s="13">
+        <f>IF($H$109="","",IF($H$109&lt;0,-$H$109/(-$H$109+100),100/($H$109+100)))</f>
+        <v/>
+      </c>
+      <c r="J109" s="16">
+        <f>IF($H$109="","",$F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))</f>
+        <v/>
+      </c>
+      <c r="K109" s="17">
+        <f>IF($H$109="","",MAX(0,($F$109*IF($H$109&lt;0,-100/$H$109,$H$109/100)-(1-$F$109))/IF($H$109&lt;0,-100/$H$109,$H$109/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L109" s="18">
+        <f>IF($H$109="","",ROUND(MIN($K$109,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M109" s="12">
+        <f>IF($J$109="","",IF($J$109&lt;0,"Pass",IF($J$109&lt;'Settings'!$B$4,"Thin",IF($J$109&lt;0.06,"✅ Sharp band",IF($J$109&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N109" s="19" t="inlineStr">
+        <is>
+          <t>Model 40.5% (fair +147). Your call.</t>
+        </is>
+      </c>
+      <c r="O109" s="15" t="n"/>
+      <c r="P109" s="16">
+        <f>IF(OR($H$109="",$O$109=""),"",(1+IF($H$109&lt;0,-100/$H$109,$H$109/100))/(1+IF($O$109&lt;0,-100/$O$109,$O$109/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B110" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E110" s="20" t="inlineStr">
+        <is>
+          <t>San Diego Padres</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="G110" s="14" t="n">
+        <v>-147</v>
+      </c>
+      <c r="H110" s="15" t="n"/>
+      <c r="I110" s="13">
+        <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
+        <v/>
+      </c>
+      <c r="J110" s="16">
+        <f>IF($H$110="","",$F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF($H$110="","",MAX(0,($F$110*IF($H$110&lt;0,-100/$H$110,$H$110/100)-(1-$F$110))/IF($H$110&lt;0,-100/$H$110,$H$110/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L110" s="18">
+        <f>IF($H$110="","",ROUND(MIN($K$110,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M110" s="12">
+        <f>IF($J$110="","",IF($J$110&lt;0,"Pass",IF($J$110&lt;'Settings'!$B$4,"Thin",IF($J$110&lt;0.06,"✅ Sharp band",IF($J$110&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N110" s="19" t="inlineStr">
+        <is>
+          <t>Model 59.5% (fair -147). Your call.</t>
+        </is>
+      </c>
+      <c r="O110" s="15" t="n"/>
+      <c r="P110" s="16">
+        <f>IF(OR($H$110="",$O$110=""),"",(1+IF($H$110&lt;0,-100/$H$110,$H$110/100))/(1+IF($O$110&lt;0,-100/$O$110,$O$110/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="G111" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="H111" s="15" t="n"/>
+      <c r="I111" s="13">
+        <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
+        <v/>
+      </c>
+      <c r="J111" s="16">
+        <f>IF($H$111="","",$F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))</f>
+        <v/>
+      </c>
+      <c r="K111" s="17">
+        <f>IF($H$111="","",MAX(0,($F$111*IF($H$111&lt;0,-100/$H$111,$H$111/100)-(1-$F$111))/IF($H$111&lt;0,-100/$H$111,$H$111/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L111" s="18">
+        <f>IF($H$111="","",ROUND(MIN($K$111,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M111" s="12">
+        <f>IF($J$111="","",IF($J$111&lt;0,"Pass",IF($J$111&lt;'Settings'!$B$4,"Thin",IF($J$111&lt;0.06,"✅ Sharp band",IF($J$111&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N111" s="19" t="inlineStr">
+        <is>
+          <t>Model 46.2% (fair +116). Your call.</t>
+        </is>
+      </c>
+      <c r="O111" s="15" t="n"/>
+      <c r="P111" s="16">
+        <f>IF(OR($H$111="",$O$111=""),"",(1+IF($H$111&lt;0,-100/$H$111,$H$111/100))/(1+IF($O$111&lt;0,-100/$O$111,$O$111/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B112" s="20" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="C112" s="20" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E112" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="G112" s="14" t="n">
+        <v>-116</v>
+      </c>
+      <c r="H112" s="15" t="n"/>
+      <c r="I112" s="13">
+        <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
+        <v/>
+      </c>
+      <c r="J112" s="16">
+        <f>IF($H$112="","",$F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))</f>
+        <v/>
+      </c>
+      <c r="K112" s="17">
+        <f>IF($H$112="","",MAX(0,($F$112*IF($H$112&lt;0,-100/$H$112,$H$112/100)-(1-$F$112))/IF($H$112&lt;0,-100/$H$112,$H$112/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L112" s="18">
+        <f>IF($H$112="","",ROUND(MIN($K$112,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M112" s="12">
+        <f>IF($J$112="","",IF($J$112&lt;0,"Pass",IF($J$112&lt;'Settings'!$B$4,"Thin",IF($J$112&lt;0.06,"✅ Sharp band",IF($J$112&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N112" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.8% (fair -116). Your call.</t>
+        </is>
+      </c>
+      <c r="O112" s="15" t="n"/>
+      <c r="P112" s="16">
+        <f>IF(OR($H$112="",$O$112=""),"",(1+IF($H$112&lt;0,-100/$H$112,$H$112/100))/(1+IF($O$112&lt;0,-100/$O$112,$O$112/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="G113" s="14" t="n">
+        <v>163</v>
+      </c>
+      <c r="H113" s="15" t="n"/>
+      <c r="I113" s="13">
+        <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
+        <v/>
+      </c>
+      <c r="J113" s="16">
+        <f>IF($H$113="","",$F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF($H$113="","",MAX(0,($F$113*IF($H$113&lt;0,-100/$H$113,$H$113/100)-(1-$F$113))/IF($H$113&lt;0,-100/$H$113,$H$113/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L113" s="18">
+        <f>IF($H$113="","",ROUND(MIN($K$113,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M113" s="12">
+        <f>IF($J$113="","",IF($J$113&lt;0,"Pass",IF($J$113&lt;'Settings'!$B$4,"Thin",IF($J$113&lt;0.06,"✅ Sharp band",IF($J$113&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N113" s="19" t="inlineStr">
+        <is>
+          <t>Model 38.0% (fair +163). Your call.</t>
+        </is>
+      </c>
+      <c r="O113" s="15" t="n"/>
+      <c r="P113" s="16">
+        <f>IF(OR($H$113="",$O$113=""),"",(1+IF($H$113&lt;0,-100/$H$113,$H$113/100))/(1+IF($O$113&lt;0,-100/$O$113,$O$113/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B114" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E114" s="20" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="G114" s="14" t="n">
+        <v>-163</v>
+      </c>
+      <c r="H114" s="15" t="n"/>
+      <c r="I114" s="13">
+        <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
+        <v/>
+      </c>
+      <c r="J114" s="16">
+        <f>IF($H$114="","",$F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))</f>
+        <v/>
+      </c>
+      <c r="K114" s="17">
+        <f>IF($H$114="","",MAX(0,($F$114*IF($H$114&lt;0,-100/$H$114,$H$114/100)-(1-$F$114))/IF($H$114&lt;0,-100/$H$114,$H$114/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L114" s="18">
+        <f>IF($H$114="","",ROUND(MIN($K$114,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M114" s="12">
+        <f>IF($J$114="","",IF($J$114&lt;0,"Pass",IF($J$114&lt;'Settings'!$B$4,"Thin",IF($J$114&lt;0.06,"✅ Sharp band",IF($J$114&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N114" s="19" t="inlineStr">
+        <is>
+          <t>Model 62.0% (fair -163). Your call.</t>
+        </is>
+      </c>
+      <c r="O114" s="15" t="n"/>
+      <c r="P114" s="16">
+        <f>IF(OR($H$114="",$O$114=""),"",(1+IF($H$114&lt;0,-100/$H$114,$H$114/100))/(1+IF($O$114&lt;0,-100/$O$114,$O$114/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Over 9.5</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>0.47085</v>
+      </c>
+      <c r="G115" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I115" s="13">
+        <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
+        <v/>
+      </c>
+      <c r="J115" s="16">
+        <f>IF($H$115="","",$F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))</f>
+        <v/>
+      </c>
+      <c r="K115" s="17">
+        <f>IF($H$115="","",MAX(0,($F$115*IF($H$115&lt;0,-100/$H$115,$H$115/100)-(1-$F$115))/IF($H$115&lt;0,-100/$H$115,$H$115/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L115" s="18">
+        <f>IF($H$115="","",ROUND(MIN($K$115,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M115" s="12">
+        <f>IF($J$115="","",IF($J$115&lt;0,"Pass",IF($J$115&lt;'Settings'!$B$4,"Thin",IF($J$115&lt;0.06,"✅ Sharp band",IF($J$115&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N115" s="19" t="inlineStr">
+        <is>
+          <t>Model 47.1% (fair +112). Your call.</t>
+        </is>
+      </c>
+      <c r="O115" s="15" t="n"/>
+      <c r="P115" s="16">
+        <f>IF(OR($H$115="",$O$115=""),"",(1+IF($H$115&lt;0,-100/$H$115,$H$115/100))/(1+IF($O$115&lt;0,-100/$O$115,$O$115/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B116" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C116" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E116" s="20" t="inlineStr">
+        <is>
+          <t>Under 9.5</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>0.5291063063063063</v>
+      </c>
+      <c r="G116" s="14" t="n">
+        <v>-112</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I116" s="13">
+        <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
+        <v/>
+      </c>
+      <c r="J116" s="16">
+        <f>IF($H$116="","",$F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF($H$116="","",MAX(0,($F$116*IF($H$116&lt;0,-100/$H$116,$H$116/100)-(1-$F$116))/IF($H$116&lt;0,-100/$H$116,$H$116/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L116" s="18">
+        <f>IF($H$116="","",ROUND(MIN($K$116,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M116" s="12">
+        <f>IF($J$116="","",IF($J$116&lt;0,"Pass",IF($J$116&lt;'Settings'!$B$4,"Thin",IF($J$116&lt;0.06,"✅ Sharp band",IF($J$116&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N116" s="19" t="inlineStr">
+        <is>
+          <t>Model 52.9% (fair -112). Your call.</t>
+        </is>
+      </c>
+      <c r="O116" s="15" t="n"/>
+      <c r="P116" s="16">
+        <f>IF(OR($H$116="",$O$116=""),"",(1+IF($H$116&lt;0,-100/$H$116,$H$116/100))/(1+IF($O$116&lt;0,-100/$O$116,$O$116/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers -1.5</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>0.5019883720930233</v>
+      </c>
+      <c r="G117" s="14" t="n">
+        <v>-101</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>-115</v>
+      </c>
+      <c r="I117" s="13">
+        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
+        <v/>
+      </c>
+      <c r="J117" s="16">
+        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
+        <v/>
+      </c>
+      <c r="K117" s="17">
+        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L117" s="18">
+        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M117" s="12">
+        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N117" s="19" t="inlineStr">
+        <is>
+          <t>Model 50.2% (fair -101). Your call.</t>
+        </is>
+      </c>
+      <c r="O117" s="15" t="n"/>
+      <c r="P117" s="16">
+        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+        </is>
+      </c>
+      <c r="C118" s="20" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="D118" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
+        <is>
+          <t>Colorado Rockies +1.5</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>0.4980274509803921</v>
+      </c>
+      <c r="G118" s="14" t="n">
+        <v>101</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>-104</v>
+      </c>
+      <c r="I118" s="13">
+        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
+        <v/>
+      </c>
+      <c r="J118" s="16">
+        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
+        <v/>
+      </c>
+      <c r="K118" s="17">
+        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L118" s="18">
+        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M118" s="12">
+        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N118" s="19" t="inlineStr">
+        <is>
+          <t>Model 49.8% (fair +101). Your call.</t>
+        </is>
+      </c>
+      <c r="O118" s="15" t="n"/>
+      <c r="P118" s="16">
+        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J88">
+  <conditionalFormatting sqref="J5:J118">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>

--- a/data/output/workbook/2026-07-06.xlsx
+++ b/data/output/workbook/2026-07-06.xlsx
@@ -367,7 +367,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10915650"/>
+    <ext cx="10125075" cy="10763250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -547,7 +547,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="11106150"/>
+    <ext cx="10125075" cy="10677525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06 14:12</t>
+          <t>2026-07-06 16:54</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4787,174 +4787,328 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>Colorado Rockies offense vs Los Angeles Dodgers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Colorado Rockies offense vs Los Angeles Dodgers defense</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.925</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H70" s="32" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A71" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B71" s="31" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="31" t="n">
+        <v>6.596</v>
+      </c>
+      <c r="Q71" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>4.925</v>
+        <v>0.92</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="D72" s="31" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E72" s="31" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F72" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G72" s="31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H72" s="32" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L72" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M72" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N72" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O72" s="31" t="n">
-        <v>4.2</v>
+        <v>3</v>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr"/>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P72" s="31" t="n">
-        <v>3.5</v>
+        <v>0.83</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.32</v>
+        <v>8.92</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5013,392 +5167,392 @@
         </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>6.596</v>
+        <v>8.106</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>0.92</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O74" s="31" t="n">
+        <v>0.433</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>0.83</v>
+        <v>0.468</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="D75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>8.106</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="H76" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J76" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Los Angeles Dodgers offense vs Colorado Rockies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers offense vs Colorado Rockies defense</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>5.463</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H78" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B79" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D79" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E79" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F79" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G79" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H79" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I79" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J79" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K79" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L79" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M79" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N79" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O79" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P79" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q79" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A79" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B79" s="31" t="n">
+        <v>9.191000000000001</v>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="31" t="inlineStr"/>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="P79" s="31" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="Q79" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>5.463</v>
-      </c>
-      <c r="C80" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D80" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E80" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F80" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G80" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H80" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>1.553</v>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I80" s="31" t="inlineStr"/>
-      <c r="J80" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K80" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L80" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M80" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N80" s="31" t="n">
-        <v>5.6</v>
+      <c r="J80" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>5.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>9.191000000000001</v>
+        <v>8.510999999999999</v>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
@@ -5457,225 +5611,71 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.779999999999999</v>
+        <v>7.28</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="C82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.623</v>
+      </c>
+      <c r="C82" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="33" t="inlineStr">
+        <is>
+          <t>30th</t>
         </is>
       </c>
       <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.95</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>1.24</v>
+        <v>0.722</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>8.510999999999999</v>
-      </c>
-      <c r="C83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr"/>
-      <c r="J83" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B84" s="31" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="C84" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="D84" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E84" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F84" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G84" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="33" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I84" s="31" t="inlineStr"/>
-      <c r="J84" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="K84" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L84" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="N84" s="31" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="O84" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="P84" s="31" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="Q84" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5916,10 +5916,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.7401481481481481</v>
+        <v>0.7394074074074073</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-285</v>
+        <v>-284</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>170</v>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 74.0% (fair -285). Your call.</t>
+          <t>Model 73.9% (fair -284). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -5958,17 +5958,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -5978,17 +5978,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7061510791366905</v>
+        <v>0.6408888888888888</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-240</v>
+        <v>-178</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 70.6% (fair -240). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -6024,17 +6024,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.7074615384615384</v>
+        <v>0.5811870503597122</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-242</v>
+        <v>-139</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -242). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -6090,17 +6090,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6110,14 +6110,14 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6445555555555555</v>
+        <v>0.588</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-181</v>
+        <v>-143</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>170</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -6156,17 +6156,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5837410071942446</v>
+        <v>0.6316666666666667</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-140</v>
+        <v>-171</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>140</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 63.2% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -6222,7 +6222,7 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
@@ -6246,13 +6246,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5900374531835206</v>
+        <v>0.5322900763358779</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-144</v>
+        <v>-114</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -6308,17 +6308,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.6305833333333333</v>
+        <v>0.4676981132075472</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-171</v>
+        <v>114</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -6378,13 +6378,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5266812227074236</v>
+        <v>0.5255947136563877</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -6425,32 +6425,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.416241134751773</v>
+        <v>0.3706666666666666</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -6491,32 +6491,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>San Diego Padres -1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.3729392971246007</v>
+        <v>0.4188129496402877</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -6576,13 +6576,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6285101321585903</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>-169</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -6623,32 +6623,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5279245283018867</v>
+        <v>0.4120152091254753</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-112</v>
+        <v>143</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5214423076923077</v>
+        <v>0.5181250000000001</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>108</v>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6770,17 +6770,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4099619771863118</v>
+        <v>0.4743999999999999</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.3974444444444444</v>
+        <v>0.394962962962963</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>170</v>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -6906,7 +6906,7 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5469576923076922</v>
+        <v>0.5466461538461538</v>
       </c>
       <c r="G20" s="14" t="n">
         <v>-121</v>
@@ -6948,7 +6948,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
@@ -6972,13 +6972,13 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5257000000000001</v>
+        <v>0.4921126760563381</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-111</v>
+        <v>103</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -7014,37 +7014,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4732882882882883</v>
+        <v>0.52205</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>111</v>
+        <v>-109</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5354470588235294</v>
+        <v>0.5410903846153846</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -7151,32 +7151,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4912206572769953</v>
+        <v>0.3925660377358491</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 39.3% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -7236,13 +7236,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5178712871287129</v>
+        <v>0.5179</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>-107</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -7278,37 +7278,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.523</v>
+        <v>0.5467396226415094</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-110</v>
+        <v>-121</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -7349,12 +7349,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.52055</v>
+        <v>0.6163800000000001</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-109</v>
+        <v>-161</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>-150</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 61.6% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -7430,17 +7430,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6130032786885246</v>
+        <v>0.4391845493562232</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-158</v>
+        <v>128</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-144</v>
+        <v>133</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -7476,37 +7476,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5271372549019607</v>
+        <v>0.5472930232558141</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-111</v>
+        <v>-121</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-104</v>
+        <v>-115</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -7563,7 +7563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6615795918367346</v>
+        <v>0.6599959183673469</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-195</v>
+        <v>-194</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-194</v>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -195). Your call.</t>
+          <t>Model 66.0% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7773,13 +7773,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3384228187919463</v>
+        <v>0.3400340136054422</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +195). Your call.</t>
+          <t>Model 34.0% (fair +194). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7835,17 +7835,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-130</v>
+        <v>156</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 39.0% (fair +156). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7901,17 +7901,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.4350000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>130</v>
+        <v>-156</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 61.0% (fair -156). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7971,13 +7971,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4732882882882883</v>
+        <v>0.4743999999999999</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>111</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5266812227074236</v>
+        <v>0.5255947136563877</v>
       </c>
       <c r="G10" s="14" t="n">
         <v>-111</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8103,13 +8103,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5257000000000001</v>
+        <v>0.5467396226415094</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-111</v>
+        <v>-121</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>100</v>
+        <v>-112</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8169,13 +8169,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4742980099502487</v>
+        <v>0.4532407407407407</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-101</v>
+        <v>116</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8235,10 +8235,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5514</v>
+        <v>0.5491</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-123</v>
+        <v>-122</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>113</v>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4486</v>
+        <v>0.4509</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays -1.5</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.2938571428571429</v>
+        <v>0.4798543689320389</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>180</v>
+        <v>106</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 29.4% (fair +240). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8414,32 +8414,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.7061510791366905</v>
+        <v>0.5201203883495146</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-240</v>
+        <v>-108</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>178</v>
+        <v>-106</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 70.6% (fair -240). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8490,22 +8490,22 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.480873786407767</v>
+        <v>0.555</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>108</v>
+        <v>-125</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8556,22 +8556,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5191309178743961</v>
+        <v>0.445</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-108</v>
+        <v>125</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-107</v>
+        <v>108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -8622,22 +8622,22 @@
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5476</v>
+        <v>0.4120152091254753</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-121</v>
+        <v>143</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -8688,22 +8688,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4524</v>
+        <v>0.588</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>121</v>
+        <v>-143</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 58.8% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -8744,32 +8744,32 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4099619771863118</v>
+        <v>0.470552995391705</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>163</v>
+        <v>117</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 47.1% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8810,32 +8810,32 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5900374531835206</v>
+        <v>0.5294654377880184</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-144</v>
+        <v>-113</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>167</v>
+        <v>-117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 52.9% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8886,22 +8886,22 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4674654377880184</v>
+        <v>0.3786</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8952,22 +8952,22 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5325135135135135</v>
+        <v>0.6214</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-114</v>
+        <v>-164</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-122</v>
+        <v>125</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Atlanta Braves -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3786</v>
+        <v>0.3714828897338403</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 37.1% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9084,22 +9084,22 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6214</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-164</v>
+        <v>-169</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>125</v>
+        <v>-125</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9140,32 +9140,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.3714828897338403</v>
+        <v>0.4986620689655172</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>163</v>
+        <v>-103</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +169). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9206,32 +9206,32 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.6285101321585903</v>
+        <v>0.5013366336633663</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-169</v>
+        <v>-101</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-127</v>
+        <v>102</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9282,22 +9282,22 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4976287128712871</v>
+        <v>0.5586</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>101</v>
+        <v>-127</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-102</v>
+        <v>117</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9348,22 +9348,22 @@
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.50235</v>
+        <v>0.4414</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-101</v>
+        <v>127</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -9404,29 +9404,29 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.5555</v>
+        <v>0.4526728110599078</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>-125</v>
+        <v>121</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>117</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -9470,32 +9470,32 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.4445</v>
+        <v>0.5472930232558141</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>125</v>
+        <v>-121</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>115</v>
+        <v>-115</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -9546,22 +9546,22 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.4547906976744186</v>
+        <v>0.3454</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -9612,22 +9612,22 @@
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.5452069767441862</v>
+        <v>0.6546000000000001</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-120</v>
+        <v>-190</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-115</v>
+        <v>100</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -9678,22 +9678,22 @@
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>San Diego Padres -1.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.3417</v>
+        <v>0.4188129496402877</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>124</v>
+        <v>178</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 34.2% (fair +193). Your call.</t>
+          <t>Model 41.9% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -9744,22 +9744,22 @@
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Arizona Diamondbacks +1.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.6583</v>
+        <v>0.5811870503597122</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-193</v>
+        <v>-139</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-104</v>
+        <v>178</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 65.8% (fair -193). Your call.</t>
+          <t>Model 58.1% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -9800,32 +9800,32 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres -1.5</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.416241134751773</v>
+        <v>0.4821267326732673</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>182</v>
+        <v>-102</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -9866,32 +9866,32 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks +1.5</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5837410071942446</v>
+        <v>0.5179</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-140</v>
+        <v>-107</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>178</v>
+        <v>100</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -9942,22 +9942,22 @@
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.4821</v>
+        <v>0.3842</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>107</v>
+        <v>160</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -10008,22 +10008,22 @@
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.5178712871287129</v>
+        <v>0.6158</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-107</v>
+        <v>-160</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -10064,32 +10064,32 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.472078431372549</v>
+        <v>0.3706666666666666</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-104</v>
+        <v>215</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 37.1% (fair +170). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -10130,32 +10130,32 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5279245283018867</v>
+        <v>0.6293</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-112</v>
+        <v>-170</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>112</v>
+        <v>-217</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 62.9% (fair -170). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -10206,22 +10206,22 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 10</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.3729392971246007</v>
+        <v>0.4712</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>213</v>
+        <v>103</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 37.3% (fair +168). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -10272,22 +10272,22 @@
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Under 10</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.6270307692307692</v>
+        <v>0.5287999999999999</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-168</v>
+        <v>-112</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-212</v>
+        <v>113</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 62.7% (fair -168). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -10338,22 +10338,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Los Angeles Dodgers -1.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4727</v>
+        <v>0.4818767772511848</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-102</v>
+        <v>-111</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +112). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -10404,22 +10404,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5273</v>
+        <v>0.5181250000000001</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-112</v>
+        <v>-108</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -112). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -10455,37 +10455,37 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.478575</v>
+        <v>0.6162</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>109</v>
+        <v>-161</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-108</v>
+        <v>100</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 61.6% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -10521,37 +10521,37 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.5214423076923077</v>
+        <v>0.3837</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-109</v>
+        <v>161</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>108</v>
+        <v>163</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 38.4% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -10602,22 +10602,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.6119</v>
+        <v>0.5604</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>-158</v>
+        <v>-127</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 56.0% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -10668,22 +10668,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.3881</v>
+        <v>0.4396</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 44.0% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -10734,22 +10734,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>St. Louis Cardinals -1.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5296</v>
+        <v>0.2606071428571429</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-113</v>
+        <v>284</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 26.1% (fair +284). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4704</v>
+        <v>0.7394074074074073</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>113</v>
+        <v>-284</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 73.9% (fair -284). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -10861,27 +10861,27 @@
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.2598571428571429</v>
+        <v>0.5161</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>285</v>
+        <v>-107</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 26.0% (fair +285). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -10927,27 +10927,27 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.7401481481481481</v>
+        <v>0.4839</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-285</v>
+        <v>107</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 74.0% (fair -285). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -10998,22 +10998,22 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.512</v>
+        <v>0.6559</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>-105</v>
+        <v>-191</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -11037,7 +11037,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 65.6% (fair -191). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -11064,22 +11064,22 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.488</v>
+        <v>0.3441</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 34.4% (fair +191). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -11130,22 +11130,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>St. Louis Cardinals -1.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.6217</v>
+        <v>0.3591071428571429</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-164</v>
+        <v>178</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -164). Your call.</t>
+          <t>Model 35.9% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -11196,22 +11196,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Milwaukee Brewers +1.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.3783</v>
+        <v>0.6408888888888888</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>164</v>
+        <v>-178</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +164). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -11252,32 +11252,32 @@
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals -1.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.3554642857142857</v>
+        <v>0.5129137254901961</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>181</v>
+        <v>-105</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>180</v>
+        <v>-104</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +181). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -11318,32 +11318,32 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
+          <t>Chicago Cubs @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers +1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.6445555555555555</v>
+        <v>0.4870792079207921</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-181</v>
+        <v>105</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -11394,22 +11394,22 @@
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.5183038647342995</v>
+        <v>0.4691</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="H61" s="15" t="n">
-        <v>-107</v>
+        <v>113</v>
       </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -11460,22 +11460,22 @@
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.4816666666666667</v>
+        <v>0.5308999999999999</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="H62" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -11526,22 +11526,22 @@
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Baltimore Orioles +1.5</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4769756097560976</v>
+        <v>0.6009230769230769</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>110</v>
+        <v>-151</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>105</v>
+        <v>-160</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -11592,22 +11592,22 @@
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Chicago Cubs -1.5</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.523</v>
+        <v>0.3990833333333333</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-110</v>
+        <v>151</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -11648,32 +11648,32 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Baltimore Orioles +1.5</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.6007121212121211</v>
+        <v>0.394962962962963</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-150</v>
+        <v>153</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>-164</v>
+        <v>170</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -150). Your call.</t>
+          <t>Model 39.5% (fair +153). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -11714,32 +11714,32 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Baltimore Orioles</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs -1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.39925</v>
+        <v>0.6050079136690647</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>150</v>
+        <v>-153</v>
       </c>
       <c r="H66" s="15" t="n">
-        <v>140</v>
+        <v>-178</v>
       </c>
       <c r="I66" s="13">
         <f>IF($H$66="","",IF($H$66&lt;0,-$H$66/(-$H$66+100),100/($H$66+100)))</f>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +150). Your call.</t>
+          <t>Model 60.5% (fair -153). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -11790,22 +11790,22 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.3974444444444444</v>
+        <v>0.618</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>152</v>
+        <v>-162</v>
       </c>
       <c r="H67" s="15" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="I67" s="13">
         <f>IF($H$67="","",IF($H$67&lt;0,-$H$67/(-$H$67+100),100/($H$67+100)))</f>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 39.7% (fair +152). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -11856,22 +11856,22 @@
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.6025748201438849</v>
+        <v>0.382</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>-152</v>
+        <v>162</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>-178</v>
+        <v>100</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 60.3% (fair -152). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -11922,22 +11922,22 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Detroit Tigers -1.5</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5271372549019607</v>
+        <v>0.4387727272727273</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-111</v>
+        <v>128</v>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-104</v>
+        <v>120</v>
       </c>
       <c r="I69" s="13">
         <f>IF($H$69="","",IF($H$69&lt;0,-$H$69/(-$H$69+100),100/($H$69+100)))</f>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -11988,22 +11988,22 @@
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4728428571428572</v>
+        <v>0.561204347826087</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>111</v>
+        <v>-128</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-110</v>
+        <v>-130</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
@@ -12054,22 +12054,22 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers -1.5</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4406481481481481</v>
+        <v>0.4372246696035242</v>
       </c>
       <c r="G71" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="H71" s="15" t="n">
         <v>127</v>
-      </c>
-      <c r="H71" s="15" t="n">
-        <v>116</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Atlanta Braves @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
@@ -12120,22 +12120,22 @@
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5593888888888888</v>
+        <v>0.5627722466960353</v>
       </c>
       <c r="G72" s="14" t="n">
+        <v>-129</v>
+      </c>
+      <c r="H72" s="15" t="n">
         <v>-127</v>
-      </c>
-      <c r="H72" s="15" t="n">
-        <v>-125</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.4384581497797357</v>
+        <v>0.4779411764705882</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>127</v>
+        <v>-104</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 43.8% (fair +128). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ Pittsburgh Pirates</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
@@ -12257,17 +12257,17 @@
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5615297297297297</v>
+        <v>0.52205</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-128</v>
+        <v>-109</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>-122</v>
+        <v>100</v>
       </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 56.2% (fair -128). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -12323,17 +12323,17 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4794705882352941</v>
+        <v>0.4921126760563381</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>-104</v>
+        <v>113</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -12357,7 +12357,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
@@ -12389,17 +12389,17 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Tampa Bay Rays</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.52055</v>
+        <v>0.5079164319248827</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-109</v>
+        <v>-103</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>100</v>
+        <v>-113</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -12423,7 +12423,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -12440,12 +12440,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -12455,17 +12455,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4912206572769953</v>
+        <v>0.4533809523809523</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -12489,7 +12489,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -12506,12 +12506,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -12521,17 +12521,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Tampa Bay Rays</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5087652582159624</v>
+        <v>0.5466461538461538</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-104</v>
+        <v>-121</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -12582,22 +12582,22 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.453047619047619</v>
+        <v>0.5312</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>121</v>
+        <v>-113</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 53.1% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -12648,22 +12648,22 @@
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5469576923076922</v>
+        <v>0.4688</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-121</v>
+        <v>113</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-108</v>
+        <v>105</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -12687,7 +12687,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 46.9% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -12714,22 +12714,22 @@
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5161254901960783</v>
+        <v>0.4676981132075472</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-107</v>
+        <v>114</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>-104</v>
+        <v>165</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -12753,7 +12753,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -12780,22 +12780,22 @@
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4839024390243903</v>
+        <v>0.5322900763358779</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>107</v>
+        <v>-114</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>105</v>
+        <v>162</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -12836,32 +12836,32 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals +1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.7074615384615384</v>
+        <v>0.4391845493562232</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-242</v>
+        <v>128</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 70.7% (fair -242). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -12902,32 +12902,32 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Kansas City Royals @ New York Mets</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros -1.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.2925572519083969</v>
+        <v>0.5608134453781511</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>242</v>
+        <v>-128</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>162</v>
+        <v>-138</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 29.3% (fair +242). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -12968,7 +12968,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -12983,17 +12983,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4366094420600858</v>
+        <v>0.6163800000000001</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>129</v>
+        <v>-161</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>133</v>
+        <v>-150</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 61.6% (fair -161). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>Philadelphia Phillies @ Cincinnati Reds</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
@@ -13049,17 +13049,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5634295081967213</v>
+        <v>0.3836065573770492</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-129</v>
+        <v>161</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-144</v>
+        <v>144</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 38.4% (fair +161). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -13110,22 +13110,22 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.6130032786885246</v>
+        <v>0.5182</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-158</v>
+        <v>-108</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>-144</v>
+        <v>113</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -13149,7 +13149,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 61.3% (fair -158). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -13176,22 +13176,22 @@
       </c>
       <c r="D88" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.3870081967213115</v>
+        <v>0.4818</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 38.7% (fair +158). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -13232,32 +13232,32 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.5065</v>
+        <v>0.4588942307692307</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>-103</v>
+        <v>118</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -103). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -13298,32 +13298,32 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.4934954954954955</v>
+        <v>0.5410903846153846</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>103</v>
+        <v>-118</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-122</v>
+        <v>-108</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 49.3% (fair +103). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -13374,22 +13374,22 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4645588235294117</v>
+        <v>0.5035499999999999</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>115</v>
+        <v>-101</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 50.4% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -13440,22 +13440,22 @@
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5354470588235294</v>
+        <v>0.4964707317073171</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-115</v>
+        <v>101</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 49.6% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -13506,22 +13506,22 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5211904761904762</v>
+        <v>0.3925660377358491</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-109</v>
+        <v>155</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-110</v>
+        <v>165</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 39.3% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -13572,22 +13572,22 @@
       </c>
       <c r="D94" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4788346153846154</v>
+        <v>0.6074103448275863</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>109</v>
+        <v>-155</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-108</v>
+        <v>-190</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 60.7% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -13628,7 +13628,7 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -13638,23 +13638,21 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins +1.5</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.6646704918032786</v>
+        <v>0.4948</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-198</v>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>-205</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H95" s="15" t="n"/>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
         <v/>
@@ -13677,7 +13675,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 66.5% (fair -198). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -13694,7 +13692,7 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
@@ -13704,23 +13702,21 @@
       </c>
       <c r="D96" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians -1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.3353358208955224</v>
+        <v>0.5052</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>198</v>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>168</v>
-      </c>
+        <v>-102</v>
+      </c>
+      <c r="H96" s="15" t="n"/>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
         <v/>
@@ -13743,7 +13739,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 33.5% (fair +198). Your call.</t>
+          <t>Model 50.5% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -13770,21 +13766,23 @@
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4973</v>
+        <v>0.5164</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="H97" s="15" t="n"/>
+        <v>-107</v>
+      </c>
+      <c r="H97" s="15" t="n">
+        <v>104</v>
+      </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
         <v/>
@@ -13807,7 +13805,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -13834,21 +13832,23 @@
       </c>
       <c r="D98" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5027</v>
+        <v>0.4836</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-101</v>
-      </c>
-      <c r="H98" s="15" t="n"/>
+        <v>107</v>
+      </c>
+      <c r="H98" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
         <v/>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -13898,22 +13898,22 @@
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Over 8</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5113433962264151</v>
+        <v>0.3683333333333333</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-105</v>
+        <v>171</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-112</v>
+        <v>140</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 36.8% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -13964,22 +13964,22 @@
       </c>
       <c r="D100" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Boston Red Sox +1.5</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.4886853658536585</v>
+        <v>0.6316666666666667</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>105</v>
+        <v>-171</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-105</v>
+        <v>140</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 63.2% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -14020,33 +14020,31 @@
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.3694166666666667</v>
+        <v>0.4778</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>171</v>
-      </c>
-      <c r="H101" s="15" t="n">
-        <v>140</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="H101" s="15" t="n"/>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
         <v/>
@@ -14069,7 +14067,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -14086,33 +14084,31 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox @ Chicago White Sox</t>
+          <t>Los Angeles Angels @ Texas Rangers</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D102" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E102" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox +1.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.6305833333333333</v>
+        <v>0.5222</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-171</v>
-      </c>
-      <c r="H102" s="15" t="n">
-        <v>140</v>
-      </c>
+        <v>-109</v>
+      </c>
+      <c r="H102" s="15" t="n"/>
       <c r="I102" s="13">
         <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
         <v/>
@@ -14135,7 +14131,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 63.1% (fair -171). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -14162,21 +14158,23 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.4738</v>
+        <v>0.5642</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H103" s="15" t="n"/>
+        <v>-129</v>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
         <v/>
@@ -14199,7 +14197,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -14226,21 +14224,23 @@
       </c>
       <c r="D104" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E104" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.5262</v>
+        <v>0.4358</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H104" s="15" t="n"/>
+        <v>129</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
         <v/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 43.6% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -14290,22 +14290,22 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Over 7</t>
+          <t>Texas Rangers -1.5</t>
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.5567821428571429</v>
+        <v>0.4004132231404959</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>-126</v>
+        <v>150</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>-124</v>
+        <v>142</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 40.0% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -14356,22 +14356,22 @@
       </c>
       <c r="D106" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>Under 7</t>
+          <t>Los Angeles Angels +1.5</t>
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.4432178217821782</v>
+        <v>0.5995897959183674</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>126</v>
+        <v>-150</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>102</v>
+        <v>-145</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 60.0% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -14412,33 +14412,31 @@
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers -1.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4032478632478633</v>
+        <v>0.4053</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="H107" s="15" t="n">
-        <v>134</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="H107" s="15" t="n"/>
       <c r="I107" s="13">
         <f>IF($H$107="","",IF($H$107&lt;0,-$H$107/(-$H$107+100),100/($H$107+100)))</f>
         <v/>
@@ -14461,7 +14459,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 40.3% (fair +148). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -14478,33 +14476,31 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Texas Rangers</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D108" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E108" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels +1.5</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5967412213740457</v>
+        <v>0.5947</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-148</v>
-      </c>
-      <c r="H108" s="15" t="n">
-        <v>-162</v>
-      </c>
+        <v>-147</v>
+      </c>
+      <c r="H108" s="15" t="n"/>
       <c r="I108" s="13">
         <f>IF($H$108="","",IF($H$108&lt;0,-$H$108/(-$H$108+100),100/($H$108+100)))</f>
         <v/>
@@ -14527,7 +14523,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 59.7% (fair -148). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -14544,12 +14540,12 @@
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -14559,14 +14555,14 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.4053</v>
+        <v>0.4611</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="H109" s="15" t="n"/>
       <c r="I109" s="13">
@@ -14591,7 +14587,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -14608,12 +14604,12 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D110" s="20" t="inlineStr">
@@ -14623,14 +14619,14 @@
       </c>
       <c r="E110" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.5947</v>
+        <v>0.5389</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-147</v>
+        <v>-117</v>
       </c>
       <c r="H110" s="15" t="n"/>
       <c r="I110" s="13">
@@ -14655,7 +14651,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -14672,12 +14668,12 @@
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -14687,14 +14683,14 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.462</v>
+        <v>0.3821</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="H111" s="15" t="n"/>
       <c r="I111" s="13">
@@ -14719,7 +14715,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -14736,12 +14732,12 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D112" s="20" t="inlineStr">
@@ -14751,14 +14747,14 @@
       </c>
       <c r="E112" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.538</v>
+        <v>0.6179</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-116</v>
+        <v>-162</v>
       </c>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="13">
@@ -14783,7 +14779,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -14810,21 +14806,23 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.3802</v>
+        <v>0.4587</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>163</v>
-      </c>
-      <c r="H113" s="15" t="n"/>
+        <v>118</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>113</v>
+      </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
         <v/>
@@ -14847,7 +14845,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -14874,21 +14872,23 @@
       </c>
       <c r="D114" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E114" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.6198</v>
+        <v>0.5413</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-163</v>
-      </c>
-      <c r="H114" s="15" t="n"/>
+        <v>-118</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>100</v>
+      </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
         <v/>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -14938,22 +14938,22 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Los Angeles Dodgers -1.5</t>
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.47085</v>
+        <v>0.5076728971962616</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>112</v>
+        <v>-103</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>100</v>
+        <v>-114</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 50.8% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -15004,22 +15004,22 @@
       </c>
       <c r="D116" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E116" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.5291063063063063</v>
+        <v>0.4923414634146343</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>-112</v>
+        <v>103</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-122</v>
+        <v>105</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -15052,141 +15052,9 @@
         <v/>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="12" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B117" s="12" t="inlineStr">
-        <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Los Angeles Dodgers -1.5</t>
-        </is>
-      </c>
-      <c r="F117" s="13" t="n">
-        <v>0.5019883720930233</v>
-      </c>
-      <c r="G117" s="14" t="n">
-        <v>-101</v>
-      </c>
-      <c r="H117" s="15" t="n">
-        <v>-115</v>
-      </c>
-      <c r="I117" s="13">
-        <f>IF($H$117="","",IF($H$117&lt;0,-$H$117/(-$H$117+100),100/($H$117+100)))</f>
-        <v/>
-      </c>
-      <c r="J117" s="16">
-        <f>IF($H$117="","",$F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))</f>
-        <v/>
-      </c>
-      <c r="K117" s="17">
-        <f>IF($H$117="","",MAX(0,($F$117*IF($H$117&lt;0,-100/$H$117,$H$117/100)-(1-$F$117))/IF($H$117&lt;0,-100/$H$117,$H$117/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L117" s="18">
-        <f>IF($H$117="","",ROUND(MIN($K$117,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M117" s="12">
-        <f>IF($J$117="","",IF($J$117&lt;0,"Pass",IF($J$117&lt;'Settings'!$B$4,"Thin",IF($J$117&lt;0.06,"✅ Sharp band",IF($J$117&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N117" s="19" t="inlineStr">
-        <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
-        </is>
-      </c>
-      <c r="O117" s="15" t="n"/>
-      <c r="P117" s="16">
-        <f>IF(OR($H$117="",$O$117=""),"",(1+IF($H$117&lt;0,-100/$H$117,$H$117/100))/(1+IF($O$117&lt;0,-100/$O$117,$O$117/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B118" s="20" t="inlineStr">
-        <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
-        </is>
-      </c>
-      <c r="C118" s="20" t="inlineStr">
-        <is>
-          <t>02:10</t>
-        </is>
-      </c>
-      <c r="D118" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E118" s="20" t="inlineStr">
-        <is>
-          <t>Colorado Rockies +1.5</t>
-        </is>
-      </c>
-      <c r="F118" s="13" t="n">
-        <v>0.4980274509803921</v>
-      </c>
-      <c r="G118" s="14" t="n">
-        <v>101</v>
-      </c>
-      <c r="H118" s="15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="I118" s="13">
-        <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
-        <v/>
-      </c>
-      <c r="J118" s="16">
-        <f>IF($H$118="","",$F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))</f>
-        <v/>
-      </c>
-      <c r="K118" s="17">
-        <f>IF($H$118="","",MAX(0,($F$118*IF($H$118&lt;0,-100/$H$118,$H$118/100)-(1-$F$118))/IF($H$118&lt;0,-100/$H$118,$H$118/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L118" s="18">
-        <f>IF($H$118="","",ROUND(MIN($K$118,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M118" s="12">
-        <f>IF($J$118="","",IF($J$118&lt;0,"Pass",IF($J$118&lt;'Settings'!$B$4,"Thin",IF($J$118&lt;0.06,"✅ Sharp band",IF($J$118&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N118" s="19" t="inlineStr">
-        <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
-        </is>
-      </c>
-      <c r="O118" s="15" t="n"/>
-      <c r="P118" s="16">
-        <f>IF(OR($H$118="",$O$118=""),"",(1+IF($H$118&lt;0,-100/$H$118,$H$118/100))/(1+IF($O$118&lt;0,-100/$O$118,$O$118/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J118">
+  <conditionalFormatting sqref="J5:J116">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16648,7 +16516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:Q82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16665,170 +16533,245 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="28" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Tampa Bay Rays defense</t>
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>4.688</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>2.733</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>4.688</v>
+        <v>8.109</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>2.733</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="H71" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>8</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>3.2</v>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>4.395</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>8.109</v>
+        <v>1.413</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -16882,28 +16825,28 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>1.413</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -16957,315 +16900,315 @@
         </is>
       </c>
       <c r="O73" s="31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="31" t="n">
-        <v>9.130000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="C74" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.333</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L74" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M74" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N74" s="31" t="n">
+        <v>0.4</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>6</v>
+        <v>0.433</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>7.778</v>
+        <v>0.5</v>
       </c>
       <c r="Q74" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs New York Yankees defense</t>
+      <c r="A77" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B77" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D77" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E77" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F77" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I77" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J77" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K77" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L77" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M77" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N77" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O77" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P77" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q77" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B78" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F78" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G78" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H78" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I78" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J78" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K78" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L78" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M78" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N78" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O78" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P78" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q78" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A78" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B78" s="31" t="n">
+        <v>4.671</v>
+      </c>
+      <c r="C78" s="31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="D78" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E78" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F78" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G78" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I78" s="31" t="inlineStr"/>
+      <c r="J78" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L78" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M78" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="N78" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O78" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P78" s="31" t="n">
+        <v>3.862</v>
+      </c>
+      <c r="Q78" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>4.671</v>
+        <v>8.778</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D79" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E79" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F79" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G79" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H79" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L79" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M79" s="31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="N79" s="31" t="n">
-        <v>5.05</v>
+      <c r="J79" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>4.733</v>
+        <v>12</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>3.862</v>
+        <v>7.609</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -17319,28 +17262,28 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>7.609</v>
+        <v>0.913</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D81" s="31" t="inlineStr">
         <is>
@@ -17394,150 +17337,75 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>0.913</v>
+        <v>8.435</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B82" s="31" t="n">
-        <v>7.244</v>
+        <v>0.541</v>
       </c>
       <c r="C82" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.633</v>
+      </c>
+      <c r="D82" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F82" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H82" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J82" s="33" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L82" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M82" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N82" s="31" t="n">
+        <v>0.65</v>
       </c>
       <c r="O82" s="31" t="n">
-        <v>12</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P82" s="31" t="n">
-        <v>8.435</v>
+        <v>0.52</v>
       </c>
       <c r="Q82" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B83" s="31" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="C83" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D83" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F83" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H83" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I83" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J83" s="33" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K83" s="31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L83" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M83" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N83" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O83" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P83" s="31" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-07-06.xlsx
+++ b/data/output/workbook/2026-07-06.xlsx
@@ -337,7 +337,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10648950"/>
+    <ext cx="10125075" cy="10496550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -367,7 +367,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10763250"/>
+    <ext cx="10125075" cy="10506075"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -547,7 +547,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="10677525"/>
+    <ext cx="10125075" cy="10839450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -890,7 +890,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06 16:54</t>
+          <t>2026-07-06 18:16</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4787,251 +4787,174 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>Colorado Rockies offense vs Los Angeles Dodgers defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B70" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C70" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D70" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E70" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F70" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G70" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H70" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I70" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J70" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K70" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L70" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M70" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N70" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O70" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P70" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q70" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.925</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>8.32</v>
+        <v>4.925</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6.1</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H71" s="32" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L71" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M71" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N71" s="31" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="O71" s="31" t="n">
+        <v>4.2</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>6.596</v>
+        <v>3.5</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>0.92</v>
+        <v>8.32</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -5090,25 +5013,25 @@
         </is>
       </c>
       <c r="P72" s="31" t="n">
-        <v>0.83</v>
+        <v>6.596</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.92</v>
+        <v>0.92</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
@@ -5167,315 +5090,315 @@
         </is>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.106</v>
+        <v>0.83</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="n">
+        <v>8.106</v>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B75" s="31" t="n">
         <v>0.5570000000000001</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C75" s="31" t="n">
         <v>0.7</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D75" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E75" s="31" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F75" s="31" t="n">
         <v>1.3</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G75" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="H74" s="32" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr">
+      <c r="I75" s="31" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="J75" s="35" t="inlineStr">
         <is>
           <t>18th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K75" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L75" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M75" s="31" t="n">
         <v>0.467</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N75" s="31" t="n">
         <v>0.45</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O75" s="31" t="n">
         <v>0.433</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P75" s="31" t="n">
         <v>0.468</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Los Angeles Dodgers offense vs Colorado Rockies defense</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B78" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
+      <c r="C78" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E77" s="29" t="inlineStr">
+      <c r="E78" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F77" s="29" t="inlineStr">
+      <c r="F78" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G77" s="29" t="inlineStr">
+      <c r="G78" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H77" s="29" t="inlineStr">
+      <c r="H78" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I77" s="29" t="inlineStr">
+      <c r="I78" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J77" s="29" t="inlineStr">
+      <c r="J78" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K77" s="29" t="inlineStr">
+      <c r="K78" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L77" s="29" t="inlineStr">
+      <c r="L78" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M77" s="29" t="inlineStr">
+      <c r="M78" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N77" s="29" t="inlineStr">
+      <c r="N78" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O77" s="29" t="inlineStr">
+      <c r="O78" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P77" s="29" t="inlineStr">
+      <c r="P78" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q77" s="29" t="inlineStr">
+      <c r="Q78" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B78" s="31" t="n">
-        <v>5.463</v>
-      </c>
-      <c r="C78" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H78" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>5.667</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="P78" s="31" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="Q78" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>9.191000000000001</v>
-      </c>
-      <c r="C79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>5.463</v>
+      </c>
+      <c r="C79" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D79" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="E79" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F79" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G79" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H79" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I79" s="31" t="inlineStr"/>
-      <c r="J79" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J79" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L79" s="31" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M79" s="31" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="N79" s="31" t="n">
+        <v>5.6</v>
       </c>
       <c r="O79" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>9.779999999999999</v>
+        <v>5.65</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>1.553</v>
+        <v>9.191000000000001</v>
       </c>
       <c r="C80" s="31" t="inlineStr">
         <is>
@@ -5534,25 +5457,25 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.24</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.510999999999999</v>
+        <v>1.553</v>
       </c>
       <c r="C81" s="31" t="inlineStr">
         <is>
@@ -5611,71 +5534,148 @@
         </is>
       </c>
       <c r="O81" s="31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>7.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="30" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B82" s="31" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="31" t="inlineStr"/>
+      <c r="J82" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P82" s="31" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="Q82" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B82" s="31" t="n">
+      <c r="B83" s="31" t="n">
         <v>0.623</v>
       </c>
-      <c r="C82" s="31" t="n">
+      <c r="C83" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D83" s="31" t="n">
         <v>0.4</v>
       </c>
-      <c r="E82" s="31" t="n">
+      <c r="E83" s="31" t="n">
         <v>0.333</v>
       </c>
-      <c r="F82" s="31" t="n">
+      <c r="F83" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="G82" s="31" t="n">
+      <c r="G83" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H83" s="33" t="inlineStr">
         <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="33" t="inlineStr">
+      <c r="I83" s="31" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr">
         <is>
           <t>26th</t>
         </is>
       </c>
-      <c r="K82" s="31" t="n">
+      <c r="K83" s="31" t="n">
         <v>1.2</v>
       </c>
-      <c r="L82" s="31" t="n">
+      <c r="L83" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="M82" s="31" t="n">
+      <c r="M83" s="31" t="n">
         <v>0.867</v>
       </c>
-      <c r="N82" s="31" t="n">
+      <c r="N83" s="31" t="n">
         <v>0.95</v>
       </c>
-      <c r="O82" s="31" t="n">
+      <c r="O83" s="31" t="n">
         <v>0.733</v>
       </c>
-      <c r="P82" s="31" t="n">
+      <c r="P83" s="31" t="n">
         <v>0.722</v>
       </c>
-      <c r="Q82" s="34" t="inlineStr">
+      <c r="Q83" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6048,10 +6048,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5811870503597122</v>
+        <v>0.5837410071942446</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>178</v>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -6180,13 +6180,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.6316666666666667</v>
+        <v>0.6316393442622951</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>-171</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6242,17 +6242,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros +1.5</t>
+          <t>Cleveland Guardians +1.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5322900763358779</v>
+        <v>0.5571111111111111</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-114</v>
+        <v>-126</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -6308,17 +6308,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Houston Astros +1.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4676981132075472</v>
+        <v>0.5322962962962963</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>114</v>
+        <v>-114</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -6354,17 +6354,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Kansas City Royals</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6374,17 +6374,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5255947136563877</v>
+        <v>0.4676981132075472</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-111</v>
+        <v>114</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -6420,37 +6420,37 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.3706666666666666</v>
+        <v>0.4429056603773585</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +170). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -6491,32 +6491,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres -1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4188129496402877</v>
+        <v>0.3686119873817035</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -6557,12 +6557,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Atlanta Braves</t>
+          <t>Arizona Diamondbacks @ San Diego Padres</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -6572,17 +6572,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>San Diego Padres -1.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.4162589928057553</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-169</v>
+        <v>140</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-125</v>
+        <v>178</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -6623,12 +6623,12 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Washington Nationals</t>
+          <t>Philadelphia Phillies @ Kansas City Royals</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals -1.5</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4120152091254753</v>
+        <v>0.5030837004405286</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>143</v>
+        <v>-101</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 41.2% (fair +143). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Los Angeles Dodgers</t>
+          <t>New York Mets @ Atlanta Braves</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>02:10</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -6704,17 +6704,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5181250000000001</v>
+        <v>0.630724778761062</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-108</v>
+        <v>-171</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>108</v>
+        <v>-126</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4743999999999999</v>
+        <v>0.4968888888888888</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>125</v>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -6816,37 +6816,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Detroit Tigers</t>
+          <t>Colorado Rockies @ Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>02:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.394962962962963</v>
+        <v>0.5129107981220657</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>153</v>
+        <v>-105</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -6882,7 +6882,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
@@ -6897,22 +6897,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Washington Nationals -1.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5466461538461538</v>
+        <v>0.4120152091254753</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-121</v>
+        <v>143</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-108</v>
+        <v>163</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 41.2% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Houston Astros @ Washington Nationals</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -6968,17 +6968,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4921126760563381</v>
+        <v>0.5466461538461538</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>103</v>
+        <v>-121</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>113</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Miami Marlins</t>
+          <t>Athletics @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -7034,17 +7034,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.52205</v>
+        <v>0.39893536121673</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-109</v>
+        <v>151</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -7085,12 +7085,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -7100,17 +7100,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5410903846153846</v>
+        <v>0.4921126760563381</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-118</v>
+        <v>103</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-108</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 49.2% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -7151,32 +7151,32 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians @ Minnesota Twins</t>
+          <t>Seattle Mariners @ Miami Marlins</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.3925660377358491</v>
+        <v>0.52205</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>155</v>
+        <v>-109</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>165</v>
+        <v>100</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -7212,17 +7212,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays @ San Francisco Giants</t>
+          <t>Cleveland Guardians @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -7232,17 +7232,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5179</v>
+        <v>0.5410903846153846</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-107</v>
+        <v>-118</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>-108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -7283,12 +7283,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Tampa Bay Rays</t>
+          <t>Toronto Blue Jays @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7298,17 +7298,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5467396226415094</v>
+        <v>0.5150495049504951</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-121</v>
+        <v>-106</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-112</v>
+        <v>102</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -7344,17 +7344,17 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ Cincinnati Reds</t>
+          <t>Milwaukee Brewers @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.6163800000000001</v>
+        <v>0.4899047619047618</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-161</v>
+        <v>104</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-150</v>
+        <v>110</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -7410,17 +7410,17 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ New York Mets</t>
+          <t>New York Yankees @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -7430,17 +7430,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4391845493562232</v>
+        <v>0.5479990654205606</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>128</v>
+        <v>-121</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>133</v>
+        <v>-114</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -7476,37 +7476,37 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ San Diego Padres</t>
+          <t>Boston Red Sox @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5472930232558141</v>
+        <v>0.5017560975609756</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-121</v>
+        <v>-101</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>-115</v>
+        <v>105</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -7707,10 +7707,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6599959183673469</v>
+        <v>0.6542551020408164</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-194</v>
+        <v>-189</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-194</v>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 66.0% (fair -194). Your call.</t>
+          <t>Model 65.4% (fair -189). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3400340136054422</v>
+        <v>0.3457482993197279</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>194</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 34.0% (fair +194). Your call.</t>
+          <t>Model 34.6% (fair +189). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -7839,13 +7839,13 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.39</v>
+        <v>0.4013</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +156). Your call.</t>
+          <t>Model 40.1% (fair +149). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -7905,10 +7905,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.61</v>
+        <v>0.5987</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-156</v>
+        <v>-149</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>113</v>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 61.0% (fair -156). Your call.</t>
+          <t>Model 59.9% (fair -149). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -7971,10 +7971,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4743999999999999</v>
+        <v>0.4968888888888888</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>125</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5255947136563877</v>
+        <v>0.5030837004405286</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-111</v>
+        <v>-101</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>127</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8103,13 +8103,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5467396226415094</v>
+        <v>0.5479990654205606</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-112</v>
+        <v>-114</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8169,13 +8169,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4532407407407407</v>
+        <v>0.452018779342723</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>121</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8199,7 +8199,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8235,13 +8235,13 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5491</v>
+        <v>0.5458</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-122</v>
+        <v>-120</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4509</v>
+        <v>0.4542</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8367,13 +8367,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4798543689320389</v>
+        <v>0.4790821256038647</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5201203883495146</v>
+        <v>0.5209436893203884</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-106</v>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8495,7 +8495,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Over 10</t>
+          <t>Over 10.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
@@ -8505,7 +8505,7 @@
         <v>-125</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 10</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
@@ -8571,7 +8571,7 @@
         <v>125</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.470552995391705</v>
+        <v>0.4732718894009216</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>117</v>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +113). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -8829,13 +8829,13 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5294654377880184</v>
+        <v>0.5267497652582159</v>
       </c>
       <c r="G22" s="14" t="n">
+        <v>-111</v>
+      </c>
+      <c r="H22" s="15" t="n">
         <v>-113</v>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>-117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -113). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -8895,10 +8895,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3786</v>
+        <v>0.381</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>122</v>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 37.9% (fair +164). Your call.</t>
+          <t>Model 38.1% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -8961,13 +8961,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.6214</v>
+        <v>0.619</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-164</v>
+        <v>-162</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 62.1% (fair -164). Your call.</t>
+          <t>Model 61.9% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9027,13 +9027,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.3714828897338403</v>
+        <v>0.3692883895131086</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +169). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9093,13 +9093,13 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.630724778761062</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-169</v>
+        <v>-171</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-125</v>
+        <v>-126</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 62.8% (fair -169). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9159,13 +9159,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4986620689655172</v>
+        <v>0.5100923076923077</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>101</v>
+        <v>-104</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-103</v>
+        <v>-108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 51.0% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9225,13 +9225,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5013366336633663</v>
+        <v>0.4899047619047618</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-101</v>
+        <v>104</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 49.0% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9291,10 +9291,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.5586</v>
+        <v>0.5555</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>-127</v>
+        <v>-125</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>117</v>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9357,13 +9357,13 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.4414</v>
+        <v>0.4445</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -9423,7 +9423,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.4526728110599078</v>
+        <v>0.4519815668202765</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>121</v>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -9489,13 +9489,13 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.5472930232558141</v>
+        <v>0.5480129032258064</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>-121</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-115</v>
+        <v>-117</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -9555,13 +9555,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3454</v>
+        <v>0.3417</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 34.2% (fair +193). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -9621,10 +9621,10 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6546000000000001</v>
+        <v>0.6583</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-190</v>
+        <v>-193</v>
       </c>
       <c r="H34" s="15" t="n">
         <v>100</v>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 65.8% (fair -193). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4188129496402877</v>
+        <v>0.4162589928057553</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>178</v>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 41.9% (fair +139). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -9753,10 +9753,10 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5811870503597122</v>
+        <v>0.5837410071942446</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-139</v>
+        <v>-140</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>178</v>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 58.1% (fair -139). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -9819,13 +9819,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4821267326732673</v>
+        <v>0.4849254901960784</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -9885,13 +9885,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5179</v>
+        <v>0.5150495049504951</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -9951,13 +9951,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.3842</v>
+        <v>0.4144</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +160). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -10017,10 +10017,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.6158</v>
+        <v>0.5856</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>-160</v>
+        <v>-141</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>108</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -160). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -10083,13 +10083,13 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.3706666666666666</v>
+        <v>0.3686119873817035</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -10113,7 +10113,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +170). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -10149,13 +10149,13 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.6293</v>
+        <v>0.6313730650154799</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-170</v>
+        <v>-171</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-217</v>
+        <v>-223</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 63.1% (fair -171). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -10221,7 +10221,7 @@
         <v>112</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -10347,13 +10347,13 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4818767772511848</v>
+        <v>0.4870671361502347</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -10413,13 +10413,13 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5181250000000001</v>
+        <v>0.5129107981220657</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-108</v>
+        <v>-105</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -11271,13 +11271,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5129137254901961</v>
+        <v>0.5160553398058252</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -11301,7 +11301,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -11337,13 +11337,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4870792079207921</v>
+        <v>0.4839705882352941</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -11535,13 +11535,13 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.6009230769230769</v>
+        <v>0.6026109375000001</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>-151</v>
+        <v>-152</v>
       </c>
       <c r="H63" s="15" t="n">
-        <v>-160</v>
+        <v>-156</v>
       </c>
       <c r="I63" s="13">
         <f>IF($H$63="","",IF($H$63&lt;0,-$H$63/(-$H$63+100),100/($H$63+100)))</f>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 60.1% (fair -151). Your call.</t>
+          <t>Model 60.3% (fair -152). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -11601,13 +11601,13 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.3990833333333333</v>
+        <v>0.3973877551020408</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H64" s="15" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="I64" s="13">
         <f>IF($H$64="","",IF($H$64&lt;0,-$H$64/(-$H$64+100),100/($H$64+100)))</f>
@@ -11631,7 +11631,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 39.9% (fair +151). Your call.</t>
+          <t>Model 39.7% (fair +152). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -11667,13 +11667,13 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.394962962962963</v>
+        <v>0.39893536121673</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H65" s="15" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="I65" s="13">
         <f>IF($H$65="","",IF($H$65&lt;0,-$H$65/(-$H$65+100),100/($H$65+100)))</f>
@@ -11697,7 +11697,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 39.9% (fair +151). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -11733,10 +11733,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.6050079136690647</v>
+        <v>0.6010381294964029</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-153</v>
+        <v>-151</v>
       </c>
       <c r="H66" s="15" t="n">
         <v>-178</v>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 60.1% (fair -151). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -11871,7 +11871,7 @@
         <v>162</v>
       </c>
       <c r="H68" s="15" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="I68" s="13">
         <f>IF($H$68="","",IF($H$68&lt;0,-$H$68/(-$H$68+100),100/($H$68+100)))</f>
@@ -12063,13 +12063,13 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.4372246696035242</v>
+        <v>0.4408108108108109</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5627722466960353</v>
+        <v>0.5591916299559472</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-129</v>
+        <v>-127</v>
       </c>
       <c r="H72" s="15" t="n">
         <v>-127</v>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -12597,7 +12597,7 @@
         <v>-113</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -12663,7 +12663,7 @@
         <v>113</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -12789,13 +12789,13 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5322900763358779</v>
+        <v>0.5322962962962963</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>-114</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -12855,13 +12855,13 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4391845493562232</v>
+        <v>0.4495594713656387</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -12921,10 +12921,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5608134453781511</v>
+        <v>0.5504344537815126</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-128</v>
+        <v>-122</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>-138</v>
@@ -12951,7 +12951,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -12987,10 +12987,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.6163800000000001</v>
+        <v>0.6138</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-161</v>
+        <v>-159</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>-150</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 61.6% (fair -161). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -13053,10 +13053,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.3836065573770492</v>
+        <v>0.386188524590164</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>144</v>
@@ -13083,7 +13083,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 38.4% (fair +161). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -13119,10 +13119,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.5182</v>
+        <v>0.5177</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>-108</v>
+        <v>-107</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>113</v>
@@ -13149,7 +13149,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 51.8% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -13185,13 +13185,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.4818</v>
+        <v>0.4823</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 48.2% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -13383,13 +13383,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.5035499999999999</v>
+        <v>0.5013411764705882</v>
       </c>
       <c r="G91" s="14" t="n">
         <v>-101</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -101). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -13449,13 +13449,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.4964707317073171</v>
+        <v>0.4986901960784313</v>
       </c>
       <c r="G92" s="14" t="n">
         <v>101</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -13479,7 +13479,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 49.6% (fair +101). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -13515,10 +13515,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3925660377358491</v>
+        <v>0.4429056603773585</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>165</v>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 39.3% (fair +155). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -13581,13 +13581,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6074103448275863</v>
+        <v>0.5571111111111111</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-155</v>
+        <v>-126</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-190</v>
+        <v>170</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 60.7% (fair -155). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -13775,13 +13775,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5164</v>
+        <v>0.5017560975609756</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-107</v>
+        <v>-101</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -13805,7 +13805,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 50.2% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -13841,13 +13841,13 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4836</v>
+        <v>0.49825</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="H98" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I98" s="13">
         <f>IF($H$98="","",IF($H$98&lt;0,-$H$98/(-$H$98+100),100/($H$98+100)))</f>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 49.8% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -13907,13 +13907,13 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.3683333333333333</v>
+        <v>0.3683606557377049</v>
       </c>
       <c r="G99" s="14" t="n">
         <v>171</v>
       </c>
       <c r="H99" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I99" s="13">
         <f>IF($H$99="","",IF($H$99&lt;0,-$H$99/(-$H$99+100),100/($H$99+100)))</f>
@@ -13973,13 +13973,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.6316666666666667</v>
+        <v>0.6316393442622951</v>
       </c>
       <c r="G100" s="14" t="n">
         <v>-171</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -14039,10 +14039,10 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.4778</v>
+        <v>0.4732</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H101" s="15" t="n"/>
       <c r="I101" s="13">
@@ -14067,7 +14067,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -14103,10 +14103,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.5222</v>
+        <v>0.5268</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-109</v>
+        <v>-111</v>
       </c>
       <c r="H102" s="15" t="n"/>
       <c r="I102" s="13">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -14167,13 +14167,13 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.5642</v>
+        <v>0.5742</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>-129</v>
+        <v>-135</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I103" s="13">
         <f>IF($H$103="","",IF($H$103&lt;0,-$H$103/(-$H$103+100),100/($H$103+100)))</f>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 57.4% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -14233,10 +14233,10 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.4358</v>
+        <v>0.4258</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>105</v>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +129). Your call.</t>
+          <t>Model 42.6% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -14299,13 +14299,13 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4004132231404959</v>
+        <v>0.3992622950819672</v>
       </c>
       <c r="G105" s="14" t="n">
         <v>150</v>
       </c>
       <c r="H105" s="15" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I105" s="13">
         <f>IF($H$105="","",IF($H$105&lt;0,-$H$105/(-$H$105+100),100/($H$105+100)))</f>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 40.0% (fair +150). Your call.</t>
+          <t>Model 39.9% (fair +150). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -14365,13 +14365,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5995897959183674</v>
+        <v>0.6007200000000001</v>
       </c>
       <c r="G106" s="14" t="n">
         <v>-150</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-145</v>
+        <v>-150</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -14395,7 +14395,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 60.0% (fair -150). Your call.</t>
+          <t>Model 60.1% (fair -150). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.3821</v>
+        <v>0.3793</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H111" s="15" t="n"/>
       <c r="I111" s="13">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 38.2% (fair +162). Your call.</t>
+          <t>Model 37.9% (fair +164). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -14751,10 +14751,10 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.6179</v>
+        <v>0.6207</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>-162</v>
+        <v>-164</v>
       </c>
       <c r="H112" s="15" t="n"/>
       <c r="I112" s="13">
@@ -14779,7 +14779,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 61.8% (fair -162). Your call.</t>
+          <t>Model 62.1% (fair -164). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -14815,10 +14815,10 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4587</v>
+        <v>0.4505</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H113" s="15" t="n">
         <v>113</v>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -14881,13 +14881,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5413</v>
+        <v>0.5495</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-118</v>
+        <v>-122</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -14947,13 +14947,13 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.5076728971962616</v>
+        <v>0.4968039215686275</v>
       </c>
       <c r="G115" s="14" t="n">
-        <v>-103</v>
+        <v>101</v>
       </c>
       <c r="H115" s="15" t="n">
-        <v>-114</v>
+        <v>-104</v>
       </c>
       <c r="I115" s="13">
         <f>IF($H$115="","",IF($H$115&lt;0,-$H$115/(-$H$115+100),100/($H$115+100)))</f>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -15013,13 +15013,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.4923414634146343</v>
+        <v>0.5032</v>
       </c>
       <c r="G116" s="14" t="n">
-        <v>103</v>
+        <v>-101</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -15158,10 +15158,10 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.2491</v>
+        <v>0.2496</v>
       </c>
       <c r="D5" s="21" t="n">
         <v>235</v>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2503</v>
+        <v>0.2508</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>196</v>
@@ -15293,7 +15293,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=314, ECE 0.055 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=315, ECE 0.057 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -15369,16 +15369,16 @@
         </is>
       </c>
       <c r="B19" s="21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" s="13" t="n">
-        <v>0.3712</v>
+        <v>0.3708</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>0.5806</v>
+        <v>0.5938</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.2094</v>
+        <v>0.223</v>
       </c>
     </row>
     <row r="20">
@@ -15596,7 +15596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15613,171 +15613,248 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs Kansas City Royals defense</t>
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.562</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>6.267</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H69" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>5.225</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.562</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>5.633</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>6.267</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>6.25</v>
+        <v>7.234</v>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>5.733</v>
+        <v>4</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>5.225</v>
+        <v>8.603999999999999</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>7.234</v>
+        <v>1.213</v>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
@@ -15836,25 +15913,25 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>8.603999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.213</v>
+        <v>8.426</v>
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
@@ -15913,317 +15990,317 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.25</v>
+        <v>8.208</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.426</v>
-      </c>
-      <c r="C73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="C73" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.75</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>11</v>
+        <v>0.867</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.208</v>
+        <v>0.805</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="32" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Kansas City Royals offense vs Philadelphia Phillies defense</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>4.533</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="32" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>4.567</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.1</v>
+        <v>7.792</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G78" s="31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
+        <v>5</v>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O78" s="31" t="n">
-        <v>4.567</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P78" s="31" t="n">
-        <v>4.75</v>
+        <v>9.319000000000001</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>7.792</v>
+        <v>0.896</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -16282,25 +16359,25 @@
         </is>
       </c>
       <c r="P79" s="31" t="n">
-        <v>9.319000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>0.896</v>
+        <v>8.021000000000001</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -16359,145 +16436,68 @@
         </is>
       </c>
       <c r="P80" s="31" t="n">
-        <v>1.17</v>
+        <v>9.276999999999999</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>8.021000000000001</v>
+        <v>0.481</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.767</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H81" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="O81" s="31" t="n">
+        <v>0.6</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>9.276999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F82" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H82" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr"/>
-      <c r="J82" s="32" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N82" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -16516,7 +16516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16533,170 +16533,245 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>New York Yankees offense vs Tampa Bay Rays defense</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="28" t="inlineStr">
-        <is>
-          <t>New York Yankees offense vs Tampa Bay Rays defense</t>
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.688</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>2.733</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>3.267</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>4.395</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B70" s="31" t="n">
-        <v>4.688</v>
+        <v>8.109</v>
       </c>
       <c r="C70" s="31" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>2.733</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="H70" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>8</v>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I70" s="31" t="inlineStr"/>
-      <c r="J70" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>3.267</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>3.2</v>
+      <c r="J70" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O70" s="31" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="P70" s="31" t="n">
-        <v>4.395</v>
+        <v>8.467000000000001</v>
       </c>
       <c r="Q70" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>8.109</v>
+        <v>1.413</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
@@ -16750,28 +16825,28 @@
         </is>
       </c>
       <c r="O71" s="31" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>8.467000000000001</v>
+        <v>1.444</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.413</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
@@ -16825,315 +16900,315 @@
         </is>
       </c>
       <c r="O72" s="31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>1.444</v>
+        <v>7.778</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>9.130000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>0.333</v>
+      </c>
+      <c r="D73" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E73" s="31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="F73" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
         </is>
       </c>
       <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L73" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M73" s="31" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="N73" s="31" t="n">
+        <v>0.4</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>6</v>
+        <v>0.433</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.778</v>
+        <v>0.5</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rays offense vs New York Yankees defense</t>
+        </is>
+      </c>
+    </row>
     <row r="76">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>Tampa Bay Rays offense vs New York Yankees defense</t>
+      <c r="A76" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B76" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C76" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D76" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E76" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F76" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G76" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H76" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I76" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J76" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K76" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L76" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M76" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N76" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O76" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P76" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q76" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B77" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D77" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E77" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F77" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G77" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H77" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I77" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J77" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K77" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L77" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M77" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N77" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O77" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P77" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q77" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A77" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B77" s="31" t="n">
+        <v>4.671</v>
+      </c>
+      <c r="C77" s="31" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="D77" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E77" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="F77" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G77" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I77" s="31" t="inlineStr"/>
+      <c r="J77" s="33" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L77" s="31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="M77" s="31" t="n">
+        <v>5.733</v>
+      </c>
+      <c r="N77" s="31" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="O77" s="31" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P77" s="31" t="n">
+        <v>3.862</v>
+      </c>
+      <c r="Q77" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B78" s="31" t="n">
-        <v>4.671</v>
+        <v>8.778</v>
       </c>
       <c r="C78" s="31" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="D78" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E78" s="31" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="F78" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="G78" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="H78" s="33" t="inlineStr">
-        <is>
-          <t>22nd</t>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="31" t="inlineStr"/>
-      <c r="J78" s="33" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="K78" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="L78" s="31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="M78" s="31" t="n">
-        <v>5.733</v>
-      </c>
-      <c r="N78" s="31" t="n">
-        <v>5.05</v>
+      <c r="J78" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O78" s="31" t="n">
-        <v>4.733</v>
+        <v>12</v>
       </c>
       <c r="P78" s="31" t="n">
-        <v>3.862</v>
+        <v>7.609</v>
       </c>
       <c r="Q78" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B79" s="31" t="n">
-        <v>8.778</v>
+        <v>0.956</v>
       </c>
       <c r="C79" s="31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D79" s="31" t="inlineStr">
         <is>
@@ -17187,28 +17262,28 @@
         </is>
       </c>
       <c r="O79" s="31" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>7.609</v>
+        <v>0.913</v>
       </c>
       <c r="Q79" s="34" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B80" s="31" t="n">
-        <v>0.956</v>
+        <v>7.244</v>
       </c>
       <c r="C80" s="31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D80" s="31" t="inlineStr">
         <is>
@@ -17262,150 +17337,75 @@
         </is>
       </c>
       <c r="O80" s="31" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P80" s="31" t="n">
-        <v>0.913</v>
+        <v>8.435</v>
       </c>
       <c r="Q80" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B81" s="31" t="n">
-        <v>7.244</v>
+        <v>0.541</v>
       </c>
       <c r="C81" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I81" s="31" t="inlineStr"/>
-      <c r="J81" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.633</v>
+      </c>
+      <c r="D81" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H81" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I81" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J81" s="33" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L81" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M81" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N81" s="31" t="n">
+        <v>0.65</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>12</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="P81" s="31" t="n">
-        <v>8.435</v>
+        <v>0.52</v>
       </c>
       <c r="Q81" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B82" s="31" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="C82" s="31" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="D82" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E82" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F82" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H82" s="35" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I82" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J82" s="33" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K82" s="31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L82" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M82" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N82" s="31" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="O82" s="31" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="P82" s="31" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="Q82" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
